--- a/玉米大豆历史数据/大豆基差/South Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/South Dakota Basis.xlsx
@@ -1900,7 +1900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1517"/>
+  <dimension ref="A1:O1517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1914,62 +1914,67 @@
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jan_Delivery</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Feb_Delivery</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mar_Delivery</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apr_Delivery</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>May_Delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jun_Delivery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jul_Delivery</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Aug_Delivery</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sep_Delivery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Oct_Delivery</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nov_Delivery</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Dec_Delivery</t>
         </is>
@@ -13598,7 +13603,6 @@
       <c r="B1454" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1454" s="7" t="n"/>
       <c r="D1454" s="7" t="n"/>
       <c r="E1454" s="7" t="n"/>
       <c r="F1454" s="7" t="n"/>
@@ -13610,6 +13614,7 @@
       <c r="L1454" s="7" t="n"/>
       <c r="M1454" s="7" t="n"/>
       <c r="N1454" s="7" t="n"/>
+      <c r="O1454" s="7" t="n"/>
     </row>
     <row r="1455">
       <c r="A1455" s="6" t="n">
@@ -13618,7 +13623,6 @@
       <c r="B1455" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1455" s="7" t="n"/>
       <c r="D1455" s="7" t="n"/>
       <c r="E1455" s="7" t="n"/>
       <c r="F1455" s="7" t="n"/>
@@ -13630,6 +13634,7 @@
       <c r="L1455" s="7" t="n"/>
       <c r="M1455" s="7" t="n"/>
       <c r="N1455" s="7" t="n"/>
+      <c r="O1455" s="7" t="n"/>
     </row>
     <row r="1456">
       <c r="A1456" s="6" t="n">
@@ -13638,7 +13643,6 @@
       <c r="B1456" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1456" s="7" t="n"/>
       <c r="D1456" s="7" t="n"/>
       <c r="E1456" s="7" t="n"/>
       <c r="F1456" s="7" t="n"/>
@@ -13650,6 +13654,7 @@
       <c r="L1456" s="7" t="n"/>
       <c r="M1456" s="7" t="n"/>
       <c r="N1456" s="7" t="n"/>
+      <c r="O1456" s="7" t="n"/>
     </row>
     <row r="1457">
       <c r="A1457" s="6" t="n">
@@ -13658,7 +13663,6 @@
       <c r="B1457" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1457" s="7" t="n"/>
       <c r="D1457" s="7" t="n"/>
       <c r="E1457" s="7" t="n"/>
       <c r="F1457" s="7" t="n"/>
@@ -13670,6 +13674,7 @@
       <c r="L1457" s="7" t="n"/>
       <c r="M1457" s="7" t="n"/>
       <c r="N1457" s="7" t="n"/>
+      <c r="O1457" s="7" t="n"/>
     </row>
     <row r="1458">
       <c r="A1458" s="6" t="n">
@@ -13678,7 +13683,6 @@
       <c r="B1458" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1458" s="7" t="n"/>
       <c r="D1458" s="7" t="n"/>
       <c r="E1458" s="7" t="n"/>
       <c r="F1458" s="7" t="n"/>
@@ -13690,6 +13694,7 @@
       <c r="L1458" s="7" t="n"/>
       <c r="M1458" s="7" t="n"/>
       <c r="N1458" s="7" t="n"/>
+      <c r="O1458" s="7" t="n"/>
     </row>
     <row r="1459">
       <c r="A1459" s="6" t="n">
@@ -13698,7 +13703,6 @@
       <c r="B1459" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1459" s="7" t="n"/>
       <c r="D1459" s="7" t="n"/>
       <c r="E1459" s="7" t="n"/>
       <c r="F1459" s="7" t="n"/>
@@ -13710,6 +13714,7 @@
       <c r="L1459" s="7" t="n"/>
       <c r="M1459" s="7" t="n"/>
       <c r="N1459" s="7" t="n"/>
+      <c r="O1459" s="7" t="n"/>
     </row>
     <row r="1460">
       <c r="A1460" s="6" t="n">
@@ -13718,7 +13723,6 @@
       <c r="B1460" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1460" s="7" t="n"/>
       <c r="D1460" s="7" t="n"/>
       <c r="E1460" s="7" t="n"/>
       <c r="F1460" s="7" t="n"/>
@@ -13730,6 +13734,7 @@
       <c r="L1460" s="7" t="n"/>
       <c r="M1460" s="7" t="n"/>
       <c r="N1460" s="7" t="n"/>
+      <c r="O1460" s="7" t="n"/>
     </row>
     <row r="1461">
       <c r="A1461" s="6" t="n">
@@ -13738,7 +13743,6 @@
       <c r="B1461" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1461" s="7" t="n"/>
       <c r="D1461" s="7" t="n"/>
       <c r="E1461" s="7" t="n"/>
       <c r="F1461" s="7" t="n"/>
@@ -13750,6 +13754,7 @@
       <c r="L1461" s="7" t="n"/>
       <c r="M1461" s="7" t="n"/>
       <c r="N1461" s="7" t="n"/>
+      <c r="O1461" s="7" t="n"/>
     </row>
     <row r="1462">
       <c r="A1462" s="6" t="n">
@@ -13758,7 +13763,6 @@
       <c r="B1462" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1462" s="7" t="n"/>
       <c r="D1462" s="7" t="n"/>
       <c r="E1462" s="7" t="n"/>
       <c r="F1462" s="7" t="n"/>
@@ -13770,6 +13774,7 @@
       <c r="L1462" s="7" t="n"/>
       <c r="M1462" s="7" t="n"/>
       <c r="N1462" s="7" t="n"/>
+      <c r="O1462" s="7" t="n"/>
     </row>
     <row r="1463">
       <c r="A1463" s="6" t="n">
@@ -13778,7 +13783,6 @@
       <c r="B1463" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1463" s="7" t="n"/>
       <c r="D1463" s="7" t="n"/>
       <c r="E1463" s="7" t="n"/>
       <c r="F1463" s="7" t="n"/>
@@ -13790,6 +13794,7 @@
       <c r="L1463" s="7" t="n"/>
       <c r="M1463" s="7" t="n"/>
       <c r="N1463" s="7" t="n"/>
+      <c r="O1463" s="7" t="n"/>
     </row>
     <row r="1464">
       <c r="A1464" s="6" t="n">
@@ -13798,7 +13803,6 @@
       <c r="B1464" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1464" s="7" t="n"/>
       <c r="D1464" s="7" t="n"/>
       <c r="E1464" s="7" t="n"/>
       <c r="F1464" s="7" t="n"/>
@@ -13810,6 +13814,7 @@
       <c r="L1464" s="7" t="n"/>
       <c r="M1464" s="7" t="n"/>
       <c r="N1464" s="7" t="n"/>
+      <c r="O1464" s="7" t="n"/>
     </row>
     <row r="1465">
       <c r="A1465" s="6" t="n">
@@ -13818,7 +13823,6 @@
       <c r="B1465" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1465" s="7" t="n"/>
       <c r="D1465" s="7" t="n"/>
       <c r="E1465" s="7" t="n"/>
       <c r="F1465" s="7" t="n"/>
@@ -13830,6 +13834,7 @@
       <c r="L1465" s="7" t="n"/>
       <c r="M1465" s="7" t="n"/>
       <c r="N1465" s="7" t="n"/>
+      <c r="O1465" s="7" t="n"/>
     </row>
     <row r="1466">
       <c r="A1466" s="6" t="n">
@@ -13838,7 +13843,6 @@
       <c r="B1466" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1466" s="7" t="n"/>
       <c r="D1466" s="7" t="n"/>
       <c r="E1466" s="7" t="n"/>
       <c r="F1466" s="7" t="n"/>
@@ -13850,6 +13854,7 @@
       <c r="L1466" s="7" t="n"/>
       <c r="M1466" s="7" t="n"/>
       <c r="N1466" s="7" t="n"/>
+      <c r="O1466" s="7" t="n"/>
     </row>
     <row r="1467">
       <c r="A1467" s="6" t="n">
@@ -13858,7 +13863,6 @@
       <c r="B1467" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1467" s="7" t="n"/>
       <c r="D1467" s="7" t="n"/>
       <c r="E1467" s="7" t="n"/>
       <c r="F1467" s="7" t="n"/>
@@ -13870,6 +13874,7 @@
       <c r="L1467" s="7" t="n"/>
       <c r="M1467" s="7" t="n"/>
       <c r="N1467" s="7" t="n"/>
+      <c r="O1467" s="7" t="n"/>
     </row>
     <row r="1468">
       <c r="A1468" s="6" t="n">
@@ -13878,7 +13883,6 @@
       <c r="B1468" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1468" s="7" t="n"/>
       <c r="D1468" s="7" t="n"/>
       <c r="E1468" s="7" t="n"/>
       <c r="F1468" s="7" t="n"/>
@@ -13890,6 +13894,7 @@
       <c r="L1468" s="7" t="n"/>
       <c r="M1468" s="7" t="n"/>
       <c r="N1468" s="7" t="n"/>
+      <c r="O1468" s="7" t="n"/>
     </row>
     <row r="1469">
       <c r="A1469" s="6" t="n">
@@ -13898,7 +13903,6 @@
       <c r="B1469" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1469" s="7" t="n"/>
       <c r="D1469" s="7" t="n"/>
       <c r="E1469" s="7" t="n"/>
       <c r="F1469" s="7" t="n"/>
@@ -13910,6 +13914,7 @@
       <c r="L1469" s="7" t="n"/>
       <c r="M1469" s="7" t="n"/>
       <c r="N1469" s="7" t="n"/>
+      <c r="O1469" s="7" t="n"/>
     </row>
     <row r="1470">
       <c r="A1470" s="6" t="n">
@@ -13918,7 +13923,6 @@
       <c r="B1470" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1470" s="7" t="n"/>
       <c r="D1470" s="7" t="n"/>
       <c r="E1470" s="7" t="n"/>
       <c r="F1470" s="7" t="n"/>
@@ -13930,6 +13934,7 @@
       <c r="L1470" s="7" t="n"/>
       <c r="M1470" s="7" t="n"/>
       <c r="N1470" s="7" t="n"/>
+      <c r="O1470" s="7" t="n"/>
     </row>
     <row r="1471">
       <c r="A1471" s="6" t="n">
@@ -13938,7 +13943,6 @@
       <c r="B1471" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1471" s="7" t="n"/>
       <c r="D1471" s="7" t="n"/>
       <c r="E1471" s="7" t="n"/>
       <c r="F1471" s="7" t="n"/>
@@ -13950,6 +13954,7 @@
       <c r="L1471" s="7" t="n"/>
       <c r="M1471" s="7" t="n"/>
       <c r="N1471" s="7" t="n"/>
+      <c r="O1471" s="7" t="n"/>
     </row>
     <row r="1472">
       <c r="A1472" s="6" t="n">
@@ -13958,7 +13963,6 @@
       <c r="B1472" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1472" s="7" t="n"/>
       <c r="D1472" s="7" t="n"/>
       <c r="E1472" s="7" t="n"/>
       <c r="F1472" s="7" t="n"/>
@@ -13970,6 +13974,7 @@
       <c r="L1472" s="7" t="n"/>
       <c r="M1472" s="7" t="n"/>
       <c r="N1472" s="7" t="n"/>
+      <c r="O1472" s="7" t="n"/>
     </row>
     <row r="1473">
       <c r="A1473" s="6" t="n">
@@ -13978,7 +13983,6 @@
       <c r="B1473" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1473" s="7" t="n"/>
       <c r="D1473" s="7" t="n"/>
       <c r="E1473" s="7" t="n"/>
       <c r="F1473" s="7" t="n"/>
@@ -13990,6 +13994,7 @@
       <c r="L1473" s="7" t="n"/>
       <c r="M1473" s="7" t="n"/>
       <c r="N1473" s="7" t="n"/>
+      <c r="O1473" s="7" t="n"/>
     </row>
     <row r="1474">
       <c r="A1474" s="6" t="n">
@@ -13998,7 +14003,6 @@
       <c r="B1474" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1474" s="7" t="n"/>
       <c r="D1474" s="7" t="n"/>
       <c r="E1474" s="7" t="n"/>
       <c r="F1474" s="7" t="n"/>
@@ -14010,6 +14014,7 @@
       <c r="L1474" s="7" t="n"/>
       <c r="M1474" s="7" t="n"/>
       <c r="N1474" s="7" t="n"/>
+      <c r="O1474" s="7" t="n"/>
     </row>
     <row r="1475">
       <c r="A1475" s="6" t="n">
@@ -14018,7 +14023,6 @@
       <c r="B1475" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1475" s="7" t="n"/>
       <c r="D1475" s="7" t="n"/>
       <c r="E1475" s="7" t="n"/>
       <c r="F1475" s="7" t="n"/>
@@ -14030,6 +14034,7 @@
       <c r="L1475" s="7" t="n"/>
       <c r="M1475" s="7" t="n"/>
       <c r="N1475" s="7" t="n"/>
+      <c r="O1475" s="7" t="n"/>
     </row>
     <row r="1476">
       <c r="A1476" s="6" t="n">
@@ -14038,7 +14043,6 @@
       <c r="B1476" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1476" s="7" t="n"/>
       <c r="D1476" s="7" t="n"/>
       <c r="E1476" s="7" t="n"/>
       <c r="F1476" s="7" t="n"/>
@@ -14050,6 +14054,7 @@
       <c r="L1476" s="7" t="n"/>
       <c r="M1476" s="7" t="n"/>
       <c r="N1476" s="7" t="n"/>
+      <c r="O1476" s="7" t="n"/>
     </row>
     <row r="1477">
       <c r="A1477" s="6" t="n">
@@ -14058,7 +14063,6 @@
       <c r="B1477" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1477" s="7" t="n"/>
       <c r="D1477" s="7" t="n"/>
       <c r="E1477" s="7" t="n"/>
       <c r="F1477" s="7" t="n"/>
@@ -14070,6 +14074,7 @@
       <c r="L1477" s="7" t="n"/>
       <c r="M1477" s="7" t="n"/>
       <c r="N1477" s="7" t="n"/>
+      <c r="O1477" s="7" t="n"/>
     </row>
     <row r="1478">
       <c r="A1478" s="6" t="n">
@@ -14078,7 +14083,6 @@
       <c r="B1478" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1478" s="7" t="n"/>
       <c r="D1478" s="7" t="n"/>
       <c r="E1478" s="7" t="n"/>
       <c r="F1478" s="7" t="n"/>
@@ -14090,6 +14094,7 @@
       <c r="L1478" s="7" t="n"/>
       <c r="M1478" s="7" t="n"/>
       <c r="N1478" s="7" t="n"/>
+      <c r="O1478" s="7" t="n"/>
     </row>
     <row r="1479">
       <c r="A1479" s="6" t="n">
@@ -14098,7 +14103,6 @@
       <c r="B1479" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1479" s="7" t="n"/>
       <c r="D1479" s="7" t="n"/>
       <c r="E1479" s="7" t="n"/>
       <c r="F1479" s="7" t="n"/>
@@ -14110,6 +14114,7 @@
       <c r="L1479" s="7" t="n"/>
       <c r="M1479" s="7" t="n"/>
       <c r="N1479" s="7" t="n"/>
+      <c r="O1479" s="7" t="n"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6" t="n">
@@ -14118,7 +14123,6 @@
       <c r="B1480" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1480" s="7" t="n"/>
       <c r="D1480" s="7" t="n"/>
       <c r="E1480" s="7" t="n"/>
       <c r="F1480" s="7" t="n"/>
@@ -14130,6 +14134,7 @@
       <c r="L1480" s="7" t="n"/>
       <c r="M1480" s="7" t="n"/>
       <c r="N1480" s="7" t="n"/>
+      <c r="O1480" s="7" t="n"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6" t="n">
@@ -14138,7 +14143,6 @@
       <c r="B1481" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1481" s="7" t="n"/>
       <c r="D1481" s="7" t="n"/>
       <c r="E1481" s="7" t="n"/>
       <c r="F1481" s="7" t="n"/>
@@ -14150,6 +14154,7 @@
       <c r="L1481" s="7" t="n"/>
       <c r="M1481" s="7" t="n"/>
       <c r="N1481" s="7" t="n"/>
+      <c r="O1481" s="7" t="n"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6" t="n">
@@ -14158,7 +14163,6 @@
       <c r="B1482" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1482" s="7" t="n"/>
       <c r="D1482" s="7" t="n"/>
       <c r="E1482" s="7" t="n"/>
       <c r="F1482" s="7" t="n"/>
@@ -14170,6 +14174,7 @@
       <c r="L1482" s="7" t="n"/>
       <c r="M1482" s="7" t="n"/>
       <c r="N1482" s="7" t="n"/>
+      <c r="O1482" s="7" t="n"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6" t="n">
@@ -14178,7 +14183,6 @@
       <c r="B1483" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1483" s="7" t="n"/>
       <c r="D1483" s="7" t="n"/>
       <c r="E1483" s="7" t="n"/>
       <c r="F1483" s="7" t="n"/>
@@ -14190,6 +14194,7 @@
       <c r="L1483" s="7" t="n"/>
       <c r="M1483" s="7" t="n"/>
       <c r="N1483" s="7" t="n"/>
+      <c r="O1483" s="7" t="n"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6" t="n">
@@ -14198,7 +14203,6 @@
       <c r="B1484" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1484" s="7" t="n"/>
       <c r="D1484" s="7" t="n"/>
       <c r="E1484" s="7" t="n"/>
       <c r="F1484" s="7" t="n"/>
@@ -14210,6 +14214,7 @@
       <c r="L1484" s="7" t="n"/>
       <c r="M1484" s="7" t="n"/>
       <c r="N1484" s="7" t="n"/>
+      <c r="O1484" s="7" t="n"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6" t="n">
@@ -14218,7 +14223,6 @@
       <c r="B1485" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1485" s="7" t="n"/>
       <c r="D1485" s="7" t="n"/>
       <c r="E1485" s="7" t="n"/>
       <c r="F1485" s="7" t="n"/>
@@ -14230,6 +14234,7 @@
       <c r="L1485" s="7" t="n"/>
       <c r="M1485" s="7" t="n"/>
       <c r="N1485" s="7" t="n"/>
+      <c r="O1485" s="7" t="n"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6" t="n">
@@ -14238,7 +14243,6 @@
       <c r="B1486" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1486" s="7" t="n"/>
       <c r="D1486" s="7" t="n"/>
       <c r="E1486" s="7" t="n"/>
       <c r="F1486" s="7" t="n"/>
@@ -14250,6 +14254,7 @@
       <c r="L1486" s="7" t="n"/>
       <c r="M1486" s="7" t="n"/>
       <c r="N1486" s="7" t="n"/>
+      <c r="O1486" s="7" t="n"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6" t="n">
@@ -14258,7 +14263,6 @@
       <c r="B1487" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1487" s="7" t="n"/>
       <c r="D1487" s="7" t="n"/>
       <c r="E1487" s="7" t="n"/>
       <c r="F1487" s="7" t="n"/>
@@ -14270,6 +14274,7 @@
       <c r="L1487" s="7" t="n"/>
       <c r="M1487" s="7" t="n"/>
       <c r="N1487" s="7" t="n"/>
+      <c r="O1487" s="7" t="n"/>
     </row>
     <row r="1488">
       <c r="A1488" s="6" t="n">
@@ -14278,7 +14283,6 @@
       <c r="B1488" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1488" s="7" t="n"/>
       <c r="D1488" s="7" t="n"/>
       <c r="E1488" s="7" t="n"/>
       <c r="F1488" s="7" t="n"/>
@@ -14290,6 +14294,7 @@
       <c r="L1488" s="7" t="n"/>
       <c r="M1488" s="7" t="n"/>
       <c r="N1488" s="7" t="n"/>
+      <c r="O1488" s="7" t="n"/>
     </row>
     <row r="1489">
       <c r="A1489" s="6" t="n">
@@ -14298,7 +14303,6 @@
       <c r="B1489" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1489" s="7" t="n"/>
       <c r="D1489" s="7" t="n"/>
       <c r="E1489" s="7" t="n"/>
       <c r="F1489" s="7" t="n"/>
@@ -14310,6 +14314,7 @@
       <c r="L1489" s="7" t="n"/>
       <c r="M1489" s="7" t="n"/>
       <c r="N1489" s="7" t="n"/>
+      <c r="O1489" s="7" t="n"/>
     </row>
     <row r="1490">
       <c r="A1490" s="6" t="n">
@@ -14318,7 +14323,6 @@
       <c r="B1490" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1490" s="7" t="n"/>
       <c r="D1490" s="7" t="n"/>
       <c r="E1490" s="7" t="n"/>
       <c r="F1490" s="7" t="n"/>
@@ -14330,6 +14334,7 @@
       <c r="L1490" s="7" t="n"/>
       <c r="M1490" s="7" t="n"/>
       <c r="N1490" s="7" t="n"/>
+      <c r="O1490" s="7" t="n"/>
     </row>
     <row r="1491">
       <c r="A1491" s="6" t="n">
@@ -14338,7 +14343,6 @@
       <c r="B1491" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1491" s="7" t="n"/>
       <c r="D1491" s="7" t="n"/>
       <c r="E1491" s="7" t="n"/>
       <c r="F1491" s="7" t="n"/>
@@ -14350,6 +14354,7 @@
       <c r="L1491" s="7" t="n"/>
       <c r="M1491" s="7" t="n"/>
       <c r="N1491" s="7" t="n"/>
+      <c r="O1491" s="7" t="n"/>
     </row>
     <row r="1492">
       <c r="A1492" s="5" t="n">
@@ -14358,7 +14363,6 @@
       <c r="B1492" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1492" s="4" t="n"/>
       <c r="D1492" s="4" t="n"/>
       <c r="E1492" s="4" t="n"/>
       <c r="F1492" s="4" t="n"/>
@@ -14370,6 +14374,7 @@
       <c r="L1492" s="4" t="n"/>
       <c r="M1492" s="4" t="n"/>
       <c r="N1492" s="4" t="n"/>
+      <c r="O1492" s="4" t="n"/>
     </row>
     <row r="1493">
       <c r="A1493" s="5" t="n">
@@ -14378,7 +14383,6 @@
       <c r="B1493" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1493" s="4" t="n"/>
       <c r="D1493" s="4" t="n"/>
       <c r="E1493" s="4" t="n"/>
       <c r="F1493" s="4" t="n"/>
@@ -14390,6 +14394,7 @@
       <c r="L1493" s="4" t="n"/>
       <c r="M1493" s="4" t="n"/>
       <c r="N1493" s="4" t="n"/>
+      <c r="O1493" s="4" t="n"/>
     </row>
     <row r="1494">
       <c r="A1494" s="5" t="n">
@@ -14398,7 +14403,6 @@
       <c r="B1494" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1494" s="4" t="n"/>
       <c r="D1494" s="4" t="n"/>
       <c r="E1494" s="4" t="n"/>
       <c r="F1494" s="4" t="n"/>
@@ -14410,6 +14414,7 @@
       <c r="L1494" s="4" t="n"/>
       <c r="M1494" s="4" t="n"/>
       <c r="N1494" s="4" t="n"/>
+      <c r="O1494" s="4" t="n"/>
     </row>
     <row r="1495">
       <c r="A1495" s="6" t="n">
@@ -14418,7 +14423,6 @@
       <c r="B1495" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1495" s="7" t="n"/>
       <c r="D1495" s="7" t="n"/>
       <c r="E1495" s="7" t="n"/>
       <c r="F1495" s="7" t="n"/>
@@ -14430,6 +14434,7 @@
       <c r="L1495" s="7" t="n"/>
       <c r="M1495" s="7" t="n"/>
       <c r="N1495" s="7" t="n"/>
+      <c r="O1495" s="7" t="n"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6" t="n">
@@ -14438,7 +14443,6 @@
       <c r="B1496" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1496" s="7" t="n"/>
       <c r="D1496" s="7" t="n"/>
       <c r="E1496" s="7" t="n"/>
       <c r="F1496" s="7" t="n"/>
@@ -14450,6 +14454,7 @@
       <c r="L1496" s="7" t="n"/>
       <c r="M1496" s="7" t="n"/>
       <c r="N1496" s="7" t="n"/>
+      <c r="O1496" s="7" t="n"/>
     </row>
     <row r="1497">
       <c r="A1497" s="5" t="n">
@@ -14458,7 +14463,6 @@
       <c r="B1497" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1497" s="4" t="n"/>
       <c r="D1497" s="4" t="n"/>
       <c r="E1497" s="4" t="n"/>
       <c r="F1497" s="4" t="n"/>
@@ -14470,6 +14474,7 @@
       <c r="L1497" s="4" t="n"/>
       <c r="M1497" s="4" t="n"/>
       <c r="N1497" s="4" t="n"/>
+      <c r="O1497" s="4" t="n"/>
     </row>
     <row r="1498">
       <c r="A1498" s="5" t="n">
@@ -14478,7 +14483,6 @@
       <c r="B1498" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1498" s="4" t="n"/>
       <c r="D1498" s="4" t="n"/>
       <c r="E1498" s="4" t="n"/>
       <c r="F1498" s="4" t="n"/>
@@ -14490,6 +14494,7 @@
       <c r="L1498" s="4" t="n"/>
       <c r="M1498" s="4" t="n"/>
       <c r="N1498" s="4" t="n"/>
+      <c r="O1498" s="4" t="n"/>
     </row>
     <row r="1499">
       <c r="A1499" s="5" t="n">
@@ -14498,7 +14503,6 @@
       <c r="B1499" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1499" s="4" t="n"/>
       <c r="D1499" s="4" t="n"/>
       <c r="E1499" s="4" t="n"/>
       <c r="F1499" s="4" t="n"/>
@@ -14510,6 +14514,7 @@
       <c r="L1499" s="4" t="n"/>
       <c r="M1499" s="4" t="n"/>
       <c r="N1499" s="4" t="n"/>
+      <c r="O1499" s="4" t="n"/>
     </row>
     <row r="1500">
       <c r="A1500" s="5" t="n">
@@ -14518,7 +14523,6 @@
       <c r="B1500" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1500" s="4" t="n"/>
       <c r="D1500" s="4" t="n"/>
       <c r="E1500" s="4" t="n"/>
       <c r="F1500" s="4" t="n"/>
@@ -14530,6 +14534,7 @@
       <c r="L1500" s="4" t="n"/>
       <c r="M1500" s="4" t="n"/>
       <c r="N1500" s="4" t="n"/>
+      <c r="O1500" s="4" t="n"/>
     </row>
     <row r="1501">
       <c r="A1501" s="6" t="n">
@@ -14538,7 +14543,6 @@
       <c r="B1501" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1501" s="7" t="n"/>
       <c r="D1501" s="7" t="n"/>
       <c r="E1501" s="7" t="n"/>
       <c r="F1501" s="7" t="n"/>
@@ -14550,6 +14554,7 @@
       <c r="L1501" s="7" t="n"/>
       <c r="M1501" s="7" t="n"/>
       <c r="N1501" s="7" t="n"/>
+      <c r="O1501" s="7" t="n"/>
     </row>
     <row r="1502">
       <c r="A1502" s="5" t="n">
@@ -14558,7 +14563,6 @@
       <c r="B1502" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1502" s="4" t="n"/>
       <c r="D1502" s="4" t="n"/>
       <c r="E1502" s="4" t="n"/>
       <c r="F1502" s="4" t="n"/>
@@ -14570,6 +14574,7 @@
       <c r="L1502" s="4" t="n"/>
       <c r="M1502" s="4" t="n"/>
       <c r="N1502" s="4" t="n"/>
+      <c r="O1502" s="4" t="n"/>
     </row>
     <row r="1503">
       <c r="A1503" s="5" t="n">
@@ -14578,7 +14583,6 @@
       <c r="B1503" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1503" s="4" t="n"/>
       <c r="D1503" s="4" t="n"/>
       <c r="E1503" s="4" t="n"/>
       <c r="F1503" s="4" t="n"/>
@@ -14590,6 +14594,7 @@
       <c r="L1503" s="4" t="n"/>
       <c r="M1503" s="4" t="n"/>
       <c r="N1503" s="4" t="n"/>
+      <c r="O1503" s="4" t="n"/>
     </row>
     <row r="1504">
       <c r="A1504" s="5" t="n">
@@ -14598,7 +14603,6 @@
       <c r="B1504" s="3" t="n">
         <v>-60</v>
       </c>
-      <c r="C1504" s="4" t="n"/>
       <c r="D1504" s="4" t="n"/>
       <c r="E1504" s="4" t="n"/>
       <c r="F1504" s="4" t="n"/>
@@ -14610,6 +14614,7 @@
       <c r="L1504" s="4" t="n"/>
       <c r="M1504" s="4" t="n"/>
       <c r="N1504" s="4" t="n"/>
+      <c r="O1504" s="4" t="n"/>
     </row>
     <row r="1505">
       <c r="A1505" s="6" t="n">
@@ -14618,7 +14623,6 @@
       <c r="B1505" s="7" t="n">
         <v>-60</v>
       </c>
-      <c r="C1505" s="7" t="n"/>
       <c r="D1505" s="7" t="n"/>
       <c r="E1505" s="7" t="n"/>
       <c r="F1505" s="7" t="n"/>
@@ -14630,6 +14634,7 @@
       <c r="L1505" s="7" t="n"/>
       <c r="M1505" s="7" t="n"/>
       <c r="N1505" s="7" t="n"/>
+      <c r="O1505" s="7" t="n"/>
     </row>
     <row r="1506">
       <c r="A1506" s="5" t="n">
@@ -14638,7 +14643,6 @@
       <c r="B1506" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1506" s="4" t="n"/>
       <c r="D1506" s="4" t="n"/>
       <c r="E1506" s="4" t="n"/>
       <c r="F1506" s="4" t="n"/>
@@ -14650,6 +14654,7 @@
       <c r="L1506" s="4" t="n"/>
       <c r="M1506" s="4" t="n"/>
       <c r="N1506" s="4" t="n"/>
+      <c r="O1506" s="4" t="n"/>
     </row>
     <row r="1507">
       <c r="A1507" s="5" t="n">
@@ -14658,7 +14663,6 @@
       <c r="B1507" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1507" s="4" t="n"/>
       <c r="D1507" s="4" t="n"/>
       <c r="E1507" s="4" t="n"/>
       <c r="F1507" s="4" t="n"/>
@@ -14670,6 +14674,7 @@
       <c r="L1507" s="4" t="n"/>
       <c r="M1507" s="4" t="n"/>
       <c r="N1507" s="4" t="n"/>
+      <c r="O1507" s="4" t="n"/>
     </row>
     <row r="1508">
       <c r="A1508" s="5" t="n">
@@ -14678,7 +14683,6 @@
       <c r="B1508" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1508" s="4" t="n"/>
       <c r="D1508" s="4" t="n"/>
       <c r="E1508" s="4" t="n"/>
       <c r="F1508" s="4" t="n"/>
@@ -14690,6 +14694,7 @@
       <c r="L1508" s="4" t="n"/>
       <c r="M1508" s="4" t="n"/>
       <c r="N1508" s="4" t="n"/>
+      <c r="O1508" s="4" t="n"/>
     </row>
     <row r="1509">
       <c r="A1509" s="5" t="n">
@@ -14698,7 +14703,6 @@
       <c r="B1509" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1509" s="4" t="n"/>
       <c r="D1509" s="4" t="n"/>
       <c r="E1509" s="4" t="n"/>
       <c r="F1509" s="4" t="n"/>
@@ -14710,6 +14714,7 @@
       <c r="L1509" s="4" t="n"/>
       <c r="M1509" s="4" t="n"/>
       <c r="N1509" s="4" t="n"/>
+      <c r="O1509" s="4" t="n"/>
     </row>
     <row r="1510">
       <c r="A1510" s="5" t="n">
@@ -14718,7 +14723,6 @@
       <c r="B1510" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1510" s="4" t="n"/>
       <c r="D1510" s="4" t="n"/>
       <c r="E1510" s="4" t="n"/>
       <c r="F1510" s="4" t="n"/>
@@ -14730,6 +14734,7 @@
       <c r="L1510" s="4" t="n"/>
       <c r="M1510" s="4" t="n"/>
       <c r="N1510" s="4" t="n"/>
+      <c r="O1510" s="4" t="n"/>
     </row>
     <row r="1511">
       <c r="A1511" s="5" t="n">
@@ -14738,7 +14743,6 @@
       <c r="B1511" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1511" s="4" t="n"/>
       <c r="D1511" s="4" t="n"/>
       <c r="E1511" s="4" t="n"/>
       <c r="F1511" s="4" t="n"/>
@@ -14750,6 +14754,7 @@
       <c r="L1511" s="4" t="n"/>
       <c r="M1511" s="4" t="n"/>
       <c r="N1511" s="4" t="n"/>
+      <c r="O1511" s="4" t="n"/>
     </row>
     <row r="1512">
       <c r="A1512" s="5" t="n">
@@ -14758,7 +14763,6 @@
       <c r="B1512" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1512" s="4" t="n"/>
       <c r="D1512" s="4" t="n"/>
       <c r="E1512" s="4" t="n"/>
       <c r="F1512" s="4" t="n"/>
@@ -14770,6 +14774,7 @@
       <c r="L1512" s="4" t="n"/>
       <c r="M1512" s="4" t="n"/>
       <c r="N1512" s="4" t="n"/>
+      <c r="O1512" s="4" t="n"/>
     </row>
     <row r="1513">
       <c r="A1513" s="5" t="n">
@@ -14778,7 +14783,6 @@
       <c r="B1513" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1513" s="4" t="n"/>
       <c r="D1513" s="4" t="n"/>
       <c r="E1513" s="4" t="n"/>
       <c r="F1513" s="4" t="n"/>
@@ -14790,6 +14794,7 @@
       <c r="L1513" s="4" t="n"/>
       <c r="M1513" s="4" t="n"/>
       <c r="N1513" s="4" t="n"/>
+      <c r="O1513" s="4" t="n"/>
     </row>
     <row r="1514">
       <c r="A1514" s="5" t="n">
@@ -14798,7 +14803,6 @@
       <c r="B1514" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1514" s="4" t="n"/>
       <c r="D1514" s="4" t="n"/>
       <c r="E1514" s="4" t="n"/>
       <c r="F1514" s="4" t="n"/>
@@ -14810,6 +14814,7 @@
       <c r="L1514" s="4" t="n"/>
       <c r="M1514" s="4" t="n"/>
       <c r="N1514" s="4" t="n"/>
+      <c r="O1514" s="4" t="n"/>
     </row>
     <row r="1515">
       <c r="A1515" s="6" t="n">
@@ -14818,7 +14823,6 @@
       <c r="B1515" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1515" s="7" t="n"/>
       <c r="D1515" s="7" t="n"/>
       <c r="E1515" s="7" t="n"/>
       <c r="F1515" s="7" t="n"/>
@@ -14830,6 +14834,7 @@
       <c r="L1515" s="7" t="n"/>
       <c r="M1515" s="7" t="n"/>
       <c r="N1515" s="7" t="n"/>
+      <c r="O1515" s="7" t="n"/>
     </row>
     <row r="1516">
       <c r="A1516" s="5" t="n">
@@ -14838,7 +14843,6 @@
       <c r="B1516" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1516" s="4" t="n"/>
       <c r="D1516" s="4" t="n"/>
       <c r="E1516" s="4" t="n"/>
       <c r="F1516" s="4" t="n"/>
@@ -14850,6 +14854,7 @@
       <c r="L1516" s="4" t="n"/>
       <c r="M1516" s="4" t="n"/>
       <c r="N1516" s="4" t="n"/>
+      <c r="O1516" s="4" t="n"/>
     </row>
     <row r="1517">
       <c r="A1517" s="8" t="n">
@@ -14857,6 +14862,9 @@
       </c>
       <c r="B1517" t="n">
         <v>-75</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14870,7 +14878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1536"/>
+  <dimension ref="A1:O1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14884,62 +14892,67 @@
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jan_Delivery</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Feb_Delivery</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mar_Delivery</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apr_Delivery</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>May_Delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jun_Delivery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jul_Delivery</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Aug_Delivery</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sep_Delivery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Oct_Delivery</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nov_Delivery</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Dec_Delivery</t>
         </is>
@@ -26720,7 +26733,6 @@
       <c r="B1473" s="7" t="n">
         <v>-41</v>
       </c>
-      <c r="C1473" s="7" t="n"/>
       <c r="D1473" s="7" t="n"/>
       <c r="E1473" s="7" t="n"/>
       <c r="F1473" s="7" t="n"/>
@@ -26732,6 +26744,7 @@
       <c r="L1473" s="7" t="n"/>
       <c r="M1473" s="7" t="n"/>
       <c r="N1473" s="7" t="n"/>
+      <c r="O1473" s="7" t="n"/>
     </row>
     <row r="1474">
       <c r="A1474" s="6" t="n">
@@ -26740,7 +26753,6 @@
       <c r="B1474" s="7" t="n">
         <v>-41</v>
       </c>
-      <c r="C1474" s="7" t="n"/>
       <c r="D1474" s="7" t="n"/>
       <c r="E1474" s="7" t="n"/>
       <c r="F1474" s="7" t="n"/>
@@ -26752,6 +26764,7 @@
       <c r="L1474" s="7" t="n"/>
       <c r="M1474" s="7" t="n"/>
       <c r="N1474" s="7" t="n"/>
+      <c r="O1474" s="7" t="n"/>
     </row>
     <row r="1475">
       <c r="A1475" s="6" t="n">
@@ -26760,7 +26773,6 @@
       <c r="B1475" s="7" t="n">
         <v>-41</v>
       </c>
-      <c r="C1475" s="7" t="n"/>
       <c r="D1475" s="7" t="n"/>
       <c r="E1475" s="7" t="n"/>
       <c r="F1475" s="7" t="n"/>
@@ -26772,6 +26784,7 @@
       <c r="L1475" s="7" t="n"/>
       <c r="M1475" s="7" t="n"/>
       <c r="N1475" s="7" t="n"/>
+      <c r="O1475" s="7" t="n"/>
     </row>
     <row r="1476">
       <c r="A1476" s="6" t="n">
@@ -26780,7 +26793,6 @@
       <c r="B1476" s="7" t="n">
         <v>-38.5</v>
       </c>
-      <c r="C1476" s="7" t="n"/>
       <c r="D1476" s="7" t="n"/>
       <c r="E1476" s="7" t="n"/>
       <c r="F1476" s="7" t="n"/>
@@ -26792,6 +26804,7 @@
       <c r="L1476" s="7" t="n"/>
       <c r="M1476" s="7" t="n"/>
       <c r="N1476" s="7" t="n"/>
+      <c r="O1476" s="7" t="n"/>
     </row>
     <row r="1477">
       <c r="A1477" s="6" t="n">
@@ -26800,7 +26813,6 @@
       <c r="B1477" s="7" t="n">
         <v>-41.5</v>
       </c>
-      <c r="C1477" s="7" t="n"/>
       <c r="D1477" s="7" t="n"/>
       <c r="E1477" s="7" t="n"/>
       <c r="F1477" s="7" t="n"/>
@@ -26812,6 +26824,7 @@
       <c r="L1477" s="7" t="n"/>
       <c r="M1477" s="7" t="n"/>
       <c r="N1477" s="7" t="n"/>
+      <c r="O1477" s="7" t="n"/>
     </row>
     <row r="1478">
       <c r="A1478" s="6" t="n">
@@ -26820,7 +26833,6 @@
       <c r="B1478" s="7" t="n">
         <v>-41.5</v>
       </c>
-      <c r="C1478" s="7" t="n"/>
       <c r="D1478" s="7" t="n"/>
       <c r="E1478" s="7" t="n"/>
       <c r="F1478" s="7" t="n"/>
@@ -26832,6 +26844,7 @@
       <c r="L1478" s="7" t="n"/>
       <c r="M1478" s="7" t="n"/>
       <c r="N1478" s="7" t="n"/>
+      <c r="O1478" s="7" t="n"/>
     </row>
     <row r="1479">
       <c r="A1479" s="6" t="n">
@@ -26840,7 +26853,6 @@
       <c r="B1479" s="7" t="n">
         <v>-38.5</v>
       </c>
-      <c r="C1479" s="7" t="n"/>
       <c r="D1479" s="7" t="n"/>
       <c r="E1479" s="7" t="n"/>
       <c r="F1479" s="7" t="n"/>
@@ -26852,6 +26864,7 @@
       <c r="L1479" s="7" t="n"/>
       <c r="M1479" s="7" t="n"/>
       <c r="N1479" s="7" t="n"/>
+      <c r="O1479" s="7" t="n"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6" t="n">
@@ -26860,7 +26873,6 @@
       <c r="B1480" s="7" t="n">
         <v>-42</v>
       </c>
-      <c r="C1480" s="7" t="n"/>
       <c r="D1480" s="7" t="n"/>
       <c r="E1480" s="7" t="n"/>
       <c r="F1480" s="7" t="n"/>
@@ -26872,6 +26884,7 @@
       <c r="L1480" s="7" t="n"/>
       <c r="M1480" s="7" t="n"/>
       <c r="N1480" s="7" t="n"/>
+      <c r="O1480" s="7" t="n"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6" t="n">
@@ -26880,7 +26893,6 @@
       <c r="B1481" s="7" t="n">
         <v>-42</v>
       </c>
-      <c r="C1481" s="7" t="n"/>
       <c r="D1481" s="7" t="n"/>
       <c r="E1481" s="7" t="n"/>
       <c r="F1481" s="7" t="n"/>
@@ -26892,6 +26904,7 @@
       <c r="L1481" s="7" t="n"/>
       <c r="M1481" s="7" t="n"/>
       <c r="N1481" s="7" t="n"/>
+      <c r="O1481" s="7" t="n"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6" t="n">
@@ -26900,7 +26913,6 @@
       <c r="B1482" s="7" t="n">
         <v>-36</v>
       </c>
-      <c r="C1482" s="7" t="n"/>
       <c r="D1482" s="7" t="n"/>
       <c r="E1482" s="7" t="n"/>
       <c r="F1482" s="7" t="n"/>
@@ -26912,6 +26924,7 @@
       <c r="L1482" s="7" t="n"/>
       <c r="M1482" s="7" t="n"/>
       <c r="N1482" s="7" t="n"/>
+      <c r="O1482" s="7" t="n"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6" t="n">
@@ -26920,7 +26933,6 @@
       <c r="B1483" s="7" t="n">
         <v>-39</v>
       </c>
-      <c r="C1483" s="7" t="n"/>
       <c r="D1483" s="7" t="n"/>
       <c r="E1483" s="7" t="n"/>
       <c r="F1483" s="7" t="n"/>
@@ -26932,6 +26944,7 @@
       <c r="L1483" s="7" t="n"/>
       <c r="M1483" s="7" t="n"/>
       <c r="N1483" s="7" t="n"/>
+      <c r="O1483" s="7" t="n"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6" t="n">
@@ -26940,7 +26953,6 @@
       <c r="B1484" s="7" t="n">
         <v>-39</v>
       </c>
-      <c r="C1484" s="7" t="n"/>
       <c r="D1484" s="7" t="n"/>
       <c r="E1484" s="7" t="n"/>
       <c r="F1484" s="7" t="n"/>
@@ -26952,6 +26964,7 @@
       <c r="L1484" s="7" t="n"/>
       <c r="M1484" s="7" t="n"/>
       <c r="N1484" s="7" t="n"/>
+      <c r="O1484" s="7" t="n"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6" t="n">
@@ -26960,7 +26973,6 @@
       <c r="B1485" s="7" t="n">
         <v>-39</v>
       </c>
-      <c r="C1485" s="7" t="n"/>
       <c r="D1485" s="7" t="n"/>
       <c r="E1485" s="7" t="n"/>
       <c r="F1485" s="7" t="n"/>
@@ -26972,6 +26984,7 @@
       <c r="L1485" s="7" t="n"/>
       <c r="M1485" s="7" t="n"/>
       <c r="N1485" s="7" t="n"/>
+      <c r="O1485" s="7" t="n"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6" t="n">
@@ -26980,7 +26993,6 @@
       <c r="B1486" s="7" t="n">
         <v>-36.5</v>
       </c>
-      <c r="C1486" s="7" t="n"/>
       <c r="D1486" s="7" t="n"/>
       <c r="E1486" s="7" t="n"/>
       <c r="F1486" s="7" t="n"/>
@@ -26992,6 +27004,7 @@
       <c r="L1486" s="7" t="n"/>
       <c r="M1486" s="7" t="n"/>
       <c r="N1486" s="7" t="n"/>
+      <c r="O1486" s="7" t="n"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6" t="n">
@@ -27000,7 +27013,6 @@
       <c r="B1487" s="7" t="n">
         <v>-36.5</v>
       </c>
-      <c r="C1487" s="7" t="n"/>
       <c r="D1487" s="7" t="n"/>
       <c r="E1487" s="7" t="n"/>
       <c r="F1487" s="7" t="n"/>
@@ -27012,6 +27024,7 @@
       <c r="L1487" s="7" t="n"/>
       <c r="M1487" s="7" t="n"/>
       <c r="N1487" s="7" t="n"/>
+      <c r="O1487" s="7" t="n"/>
     </row>
     <row r="1488">
       <c r="A1488" s="6" t="n">
@@ -27020,7 +27033,6 @@
       <c r="B1488" s="7" t="n">
         <v>-36.5</v>
       </c>
-      <c r="C1488" s="7" t="n"/>
       <c r="D1488" s="7" t="n"/>
       <c r="E1488" s="7" t="n"/>
       <c r="F1488" s="7" t="n"/>
@@ -27032,6 +27044,7 @@
       <c r="L1488" s="7" t="n"/>
       <c r="M1488" s="7" t="n"/>
       <c r="N1488" s="7" t="n"/>
+      <c r="O1488" s="7" t="n"/>
     </row>
     <row r="1489">
       <c r="A1489" s="6" t="n">
@@ -27040,7 +27053,6 @@
       <c r="B1489" s="7" t="n">
         <v>-36.5</v>
       </c>
-      <c r="C1489" s="7" t="n"/>
       <c r="D1489" s="7" t="n"/>
       <c r="E1489" s="7" t="n"/>
       <c r="F1489" s="7" t="n"/>
@@ -27052,6 +27064,7 @@
       <c r="L1489" s="7" t="n"/>
       <c r="M1489" s="7" t="n"/>
       <c r="N1489" s="7" t="n"/>
+      <c r="O1489" s="7" t="n"/>
     </row>
     <row r="1490">
       <c r="A1490" s="6" t="n">
@@ -27060,7 +27073,6 @@
       <c r="B1490" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="C1490" s="7" t="n"/>
       <c r="D1490" s="7" t="n"/>
       <c r="E1490" s="7" t="n"/>
       <c r="F1490" s="7" t="n"/>
@@ -27072,6 +27084,7 @@
       <c r="L1490" s="7" t="n"/>
       <c r="M1490" s="7" t="n"/>
       <c r="N1490" s="7" t="n"/>
+      <c r="O1490" s="7" t="n"/>
     </row>
     <row r="1491">
       <c r="A1491" s="6" t="n">
@@ -27080,7 +27093,6 @@
       <c r="B1491" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="C1491" s="7" t="n"/>
       <c r="D1491" s="7" t="n"/>
       <c r="E1491" s="7" t="n"/>
       <c r="F1491" s="7" t="n"/>
@@ -27092,6 +27104,7 @@
       <c r="L1491" s="7" t="n"/>
       <c r="M1491" s="7" t="n"/>
       <c r="N1491" s="7" t="n"/>
+      <c r="O1491" s="7" t="n"/>
     </row>
     <row r="1492">
       <c r="A1492" s="6" t="n">
@@ -27100,7 +27113,6 @@
       <c r="B1492" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="C1492" s="7" t="n"/>
       <c r="D1492" s="7" t="n"/>
       <c r="E1492" s="7" t="n"/>
       <c r="F1492" s="7" t="n"/>
@@ -27112,6 +27124,7 @@
       <c r="L1492" s="7" t="n"/>
       <c r="M1492" s="7" t="n"/>
       <c r="N1492" s="7" t="n"/>
+      <c r="O1492" s="7" t="n"/>
     </row>
     <row r="1493">
       <c r="A1493" s="6" t="n">
@@ -27120,7 +27133,6 @@
       <c r="B1493" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="C1493" s="7" t="n"/>
       <c r="D1493" s="7" t="n"/>
       <c r="E1493" s="7" t="n"/>
       <c r="F1493" s="7" t="n"/>
@@ -27132,6 +27144,7 @@
       <c r="L1493" s="7" t="n"/>
       <c r="M1493" s="7" t="n"/>
       <c r="N1493" s="7" t="n"/>
+      <c r="O1493" s="7" t="n"/>
     </row>
     <row r="1494">
       <c r="A1494" s="6" t="n">
@@ -27140,7 +27153,6 @@
       <c r="B1494" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="C1494" s="7" t="n"/>
       <c r="D1494" s="7" t="n"/>
       <c r="E1494" s="7" t="n"/>
       <c r="F1494" s="7" t="n"/>
@@ -27152,6 +27164,7 @@
       <c r="L1494" s="7" t="n"/>
       <c r="M1494" s="7" t="n"/>
       <c r="N1494" s="7" t="n"/>
+      <c r="O1494" s="7" t="n"/>
     </row>
     <row r="1495">
       <c r="A1495" s="6" t="n">
@@ -27160,7 +27173,6 @@
       <c r="B1495" s="7" t="n">
         <v>-26.5</v>
       </c>
-      <c r="C1495" s="7" t="n"/>
       <c r="D1495" s="7" t="n"/>
       <c r="E1495" s="7" t="n"/>
       <c r="F1495" s="7" t="n"/>
@@ -27172,6 +27184,7 @@
       <c r="L1495" s="7" t="n"/>
       <c r="M1495" s="7" t="n"/>
       <c r="N1495" s="7" t="n"/>
+      <c r="O1495" s="7" t="n"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6" t="n">
@@ -27180,7 +27193,6 @@
       <c r="B1496" s="7" t="n">
         <v>-26.5</v>
       </c>
-      <c r="C1496" s="7" t="n"/>
       <c r="D1496" s="7" t="n"/>
       <c r="E1496" s="7" t="n"/>
       <c r="F1496" s="7" t="n"/>
@@ -27192,6 +27204,7 @@
       <c r="L1496" s="7" t="n"/>
       <c r="M1496" s="7" t="n"/>
       <c r="N1496" s="7" t="n"/>
+      <c r="O1496" s="7" t="n"/>
     </row>
     <row r="1497">
       <c r="A1497" s="6" t="n">
@@ -27200,7 +27213,6 @@
       <c r="B1497" s="7" t="n">
         <v>-31.5</v>
       </c>
-      <c r="C1497" s="7" t="n"/>
       <c r="D1497" s="7" t="n"/>
       <c r="E1497" s="7" t="n"/>
       <c r="F1497" s="7" t="n"/>
@@ -27212,6 +27224,7 @@
       <c r="L1497" s="7" t="n"/>
       <c r="M1497" s="7" t="n"/>
       <c r="N1497" s="7" t="n"/>
+      <c r="O1497" s="7" t="n"/>
     </row>
     <row r="1498">
       <c r="A1498" s="6" t="n">
@@ -27220,7 +27233,6 @@
       <c r="B1498" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="C1498" s="7" t="n"/>
       <c r="D1498" s="7" t="n"/>
       <c r="E1498" s="7" t="n"/>
       <c r="F1498" s="7" t="n"/>
@@ -27232,6 +27244,7 @@
       <c r="L1498" s="7" t="n"/>
       <c r="M1498" s="7" t="n"/>
       <c r="N1498" s="7" t="n"/>
+      <c r="O1498" s="7" t="n"/>
     </row>
     <row r="1499">
       <c r="A1499" s="6" t="n">
@@ -27240,7 +27253,6 @@
       <c r="B1499" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="C1499" s="7" t="n"/>
       <c r="D1499" s="7" t="n"/>
       <c r="E1499" s="7" t="n"/>
       <c r="F1499" s="7" t="n"/>
@@ -27252,6 +27264,7 @@
       <c r="L1499" s="7" t="n"/>
       <c r="M1499" s="7" t="n"/>
       <c r="N1499" s="7" t="n"/>
+      <c r="O1499" s="7" t="n"/>
     </row>
     <row r="1500">
       <c r="A1500" s="6" t="n">
@@ -27260,7 +27273,6 @@
       <c r="B1500" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="C1500" s="7" t="n"/>
       <c r="D1500" s="7" t="n"/>
       <c r="E1500" s="7" t="n"/>
       <c r="F1500" s="7" t="n"/>
@@ -27272,6 +27284,7 @@
       <c r="L1500" s="7" t="n"/>
       <c r="M1500" s="7" t="n"/>
       <c r="N1500" s="7" t="n"/>
+      <c r="O1500" s="7" t="n"/>
     </row>
     <row r="1501">
       <c r="A1501" s="6" t="n">
@@ -27280,7 +27293,6 @@
       <c r="B1501" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="C1501" s="7" t="n"/>
       <c r="D1501" s="7" t="n"/>
       <c r="E1501" s="7" t="n"/>
       <c r="F1501" s="7" t="n"/>
@@ -27292,6 +27304,7 @@
       <c r="L1501" s="7" t="n"/>
       <c r="M1501" s="7" t="n"/>
       <c r="N1501" s="7" t="n"/>
+      <c r="O1501" s="7" t="n"/>
     </row>
     <row r="1502">
       <c r="A1502" s="6" t="n">
@@ -27300,7 +27313,6 @@
       <c r="B1502" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="C1502" s="7" t="n"/>
       <c r="D1502" s="7" t="n"/>
       <c r="E1502" s="7" t="n"/>
       <c r="F1502" s="7" t="n"/>
@@ -27312,6 +27324,7 @@
       <c r="L1502" s="7" t="n"/>
       <c r="M1502" s="7" t="n"/>
       <c r="N1502" s="7" t="n"/>
+      <c r="O1502" s="7" t="n"/>
     </row>
     <row r="1503">
       <c r="A1503" s="6" t="n">
@@ -27320,7 +27333,6 @@
       <c r="B1503" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="C1503" s="7" t="n"/>
       <c r="D1503" s="7" t="n"/>
       <c r="E1503" s="7" t="n"/>
       <c r="F1503" s="7" t="n"/>
@@ -27332,6 +27344,7 @@
       <c r="L1503" s="7" t="n"/>
       <c r="M1503" s="7" t="n"/>
       <c r="N1503" s="7" t="n"/>
+      <c r="O1503" s="7" t="n"/>
     </row>
     <row r="1504">
       <c r="A1504" s="6" t="n">
@@ -27340,7 +27353,6 @@
       <c r="B1504" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1504" s="7" t="n"/>
       <c r="D1504" s="7" t="n"/>
       <c r="E1504" s="7" t="n"/>
       <c r="F1504" s="7" t="n"/>
@@ -27352,6 +27364,7 @@
       <c r="L1504" s="7" t="n"/>
       <c r="M1504" s="7" t="n"/>
       <c r="N1504" s="7" t="n"/>
+      <c r="O1504" s="7" t="n"/>
     </row>
     <row r="1505">
       <c r="A1505" s="6" t="n">
@@ -27360,7 +27373,6 @@
       <c r="B1505" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1505" s="7" t="n"/>
       <c r="D1505" s="7" t="n"/>
       <c r="E1505" s="7" t="n"/>
       <c r="F1505" s="7" t="n"/>
@@ -27372,6 +27384,7 @@
       <c r="L1505" s="7" t="n"/>
       <c r="M1505" s="7" t="n"/>
       <c r="N1505" s="7" t="n"/>
+      <c r="O1505" s="7" t="n"/>
     </row>
     <row r="1506">
       <c r="A1506" s="6" t="n">
@@ -27380,7 +27393,6 @@
       <c r="B1506" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1506" s="7" t="n"/>
       <c r="D1506" s="7" t="n"/>
       <c r="E1506" s="7" t="n"/>
       <c r="F1506" s="7" t="n"/>
@@ -27392,6 +27404,7 @@
       <c r="L1506" s="7" t="n"/>
       <c r="M1506" s="7" t="n"/>
       <c r="N1506" s="7" t="n"/>
+      <c r="O1506" s="7" t="n"/>
     </row>
     <row r="1507">
       <c r="A1507" s="6" t="n">
@@ -27400,7 +27413,6 @@
       <c r="B1507" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1507" s="7" t="n"/>
       <c r="D1507" s="7" t="n"/>
       <c r="E1507" s="7" t="n"/>
       <c r="F1507" s="7" t="n"/>
@@ -27412,6 +27424,7 @@
       <c r="L1507" s="7" t="n"/>
       <c r="M1507" s="7" t="n"/>
       <c r="N1507" s="7" t="n"/>
+      <c r="O1507" s="7" t="n"/>
     </row>
     <row r="1508">
       <c r="A1508" s="6" t="n">
@@ -27420,7 +27433,6 @@
       <c r="B1508" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1508" s="7" t="n"/>
       <c r="D1508" s="7" t="n"/>
       <c r="E1508" s="7" t="n"/>
       <c r="F1508" s="7" t="n"/>
@@ -27432,6 +27444,7 @@
       <c r="L1508" s="7" t="n"/>
       <c r="M1508" s="7" t="n"/>
       <c r="N1508" s="7" t="n"/>
+      <c r="O1508" s="7" t="n"/>
     </row>
     <row r="1509">
       <c r="A1509" s="6" t="n">
@@ -27440,7 +27453,6 @@
       <c r="B1509" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1509" s="7" t="n"/>
       <c r="D1509" s="7" t="n"/>
       <c r="E1509" s="7" t="n"/>
       <c r="F1509" s="7" t="n"/>
@@ -27452,6 +27464,7 @@
       <c r="L1509" s="7" t="n"/>
       <c r="M1509" s="7" t="n"/>
       <c r="N1509" s="7" t="n"/>
+      <c r="O1509" s="7" t="n"/>
     </row>
     <row r="1510">
       <c r="A1510" s="6" t="n">
@@ -27460,7 +27473,6 @@
       <c r="B1510" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1510" s="7" t="n"/>
       <c r="D1510" s="7" t="n"/>
       <c r="E1510" s="7" t="n"/>
       <c r="F1510" s="7" t="n"/>
@@ -27472,6 +27484,7 @@
       <c r="L1510" s="7" t="n"/>
       <c r="M1510" s="7" t="n"/>
       <c r="N1510" s="7" t="n"/>
+      <c r="O1510" s="7" t="n"/>
     </row>
     <row r="1511">
       <c r="A1511" s="5" t="n">
@@ -27480,7 +27493,6 @@
       <c r="B1511" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1511" s="4" t="n"/>
       <c r="D1511" s="4" t="n"/>
       <c r="E1511" s="4" t="n"/>
       <c r="F1511" s="4" t="n"/>
@@ -27492,6 +27504,7 @@
       <c r="L1511" s="4" t="n"/>
       <c r="M1511" s="4" t="n"/>
       <c r="N1511" s="4" t="n"/>
+      <c r="O1511" s="4" t="n"/>
     </row>
     <row r="1512">
       <c r="A1512" s="5" t="n">
@@ -27500,7 +27513,6 @@
       <c r="B1512" s="3" t="n">
         <v>-60</v>
       </c>
-      <c r="C1512" s="4" t="n"/>
       <c r="D1512" s="4" t="n"/>
       <c r="E1512" s="4" t="n"/>
       <c r="F1512" s="4" t="n"/>
@@ -27512,6 +27524,7 @@
       <c r="L1512" s="4" t="n"/>
       <c r="M1512" s="4" t="n"/>
       <c r="N1512" s="4" t="n"/>
+      <c r="O1512" s="4" t="n"/>
     </row>
     <row r="1513">
       <c r="A1513" s="5" t="n">
@@ -27520,7 +27533,6 @@
       <c r="B1513" s="3" t="n">
         <v>-60</v>
       </c>
-      <c r="C1513" s="4" t="n"/>
       <c r="D1513" s="4" t="n"/>
       <c r="E1513" s="4" t="n"/>
       <c r="F1513" s="4" t="n"/>
@@ -27532,6 +27544,7 @@
       <c r="L1513" s="4" t="n"/>
       <c r="M1513" s="4" t="n"/>
       <c r="N1513" s="4" t="n"/>
+      <c r="O1513" s="4" t="n"/>
     </row>
     <row r="1514">
       <c r="A1514" s="6" t="n">
@@ -27540,7 +27553,6 @@
       <c r="B1514" s="7" t="n">
         <v>-60</v>
       </c>
-      <c r="C1514" s="7" t="n"/>
       <c r="D1514" s="7" t="n"/>
       <c r="E1514" s="7" t="n"/>
       <c r="F1514" s="7" t="n"/>
@@ -27552,6 +27564,7 @@
       <c r="L1514" s="7" t="n"/>
       <c r="M1514" s="7" t="n"/>
       <c r="N1514" s="7" t="n"/>
+      <c r="O1514" s="7" t="n"/>
     </row>
     <row r="1515">
       <c r="A1515" s="6" t="n">
@@ -27560,7 +27573,6 @@
       <c r="B1515" s="7" t="n">
         <v>-65</v>
       </c>
-      <c r="C1515" s="7" t="n"/>
       <c r="D1515" s="7" t="n"/>
       <c r="E1515" s="7" t="n"/>
       <c r="F1515" s="7" t="n"/>
@@ -27572,6 +27584,7 @@
       <c r="L1515" s="7" t="n"/>
       <c r="M1515" s="7" t="n"/>
       <c r="N1515" s="7" t="n"/>
+      <c r="O1515" s="7" t="n"/>
     </row>
     <row r="1516">
       <c r="A1516" s="5" t="n">
@@ -27580,7 +27593,6 @@
       <c r="B1516" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1516" s="4" t="n"/>
       <c r="D1516" s="4" t="n"/>
       <c r="E1516" s="4" t="n"/>
       <c r="F1516" s="4" t="n"/>
@@ -27592,6 +27604,7 @@
       <c r="L1516" s="4" t="n"/>
       <c r="M1516" s="4" t="n"/>
       <c r="N1516" s="4" t="n"/>
+      <c r="O1516" s="4" t="n"/>
     </row>
     <row r="1517">
       <c r="A1517" s="5" t="n">
@@ -27600,7 +27613,6 @@
       <c r="B1517" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1517" s="4" t="n"/>
       <c r="D1517" s="4" t="n"/>
       <c r="E1517" s="4" t="n"/>
       <c r="F1517" s="4" t="n"/>
@@ -27612,6 +27624,7 @@
       <c r="L1517" s="4" t="n"/>
       <c r="M1517" s="4" t="n"/>
       <c r="N1517" s="4" t="n"/>
+      <c r="O1517" s="4" t="n"/>
     </row>
     <row r="1518">
       <c r="A1518" s="5" t="n">
@@ -27620,7 +27633,6 @@
       <c r="B1518" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1518" s="4" t="n"/>
       <c r="D1518" s="4" t="n"/>
       <c r="E1518" s="4" t="n"/>
       <c r="F1518" s="4" t="n"/>
@@ -27632,6 +27644,7 @@
       <c r="L1518" s="4" t="n"/>
       <c r="M1518" s="4" t="n"/>
       <c r="N1518" s="4" t="n"/>
+      <c r="O1518" s="4" t="n"/>
     </row>
     <row r="1519">
       <c r="A1519" s="5" t="n">
@@ -27640,7 +27653,6 @@
       <c r="B1519" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1519" s="4" t="n"/>
       <c r="D1519" s="4" t="n"/>
       <c r="E1519" s="4" t="n"/>
       <c r="F1519" s="4" t="n"/>
@@ -27652,6 +27664,7 @@
       <c r="L1519" s="4" t="n"/>
       <c r="M1519" s="4" t="n"/>
       <c r="N1519" s="4" t="n"/>
+      <c r="O1519" s="4" t="n"/>
     </row>
     <row r="1520">
       <c r="A1520" s="6" t="n">
@@ -27660,7 +27673,6 @@
       <c r="B1520" s="7" t="n">
         <v>-65</v>
       </c>
-      <c r="C1520" s="7" t="n"/>
       <c r="D1520" s="7" t="n"/>
       <c r="E1520" s="7" t="n"/>
       <c r="F1520" s="7" t="n"/>
@@ -27672,6 +27684,7 @@
       <c r="L1520" s="7" t="n"/>
       <c r="M1520" s="7" t="n"/>
       <c r="N1520" s="7" t="n"/>
+      <c r="O1520" s="7" t="n"/>
     </row>
     <row r="1521">
       <c r="A1521" s="5" t="n">
@@ -27680,7 +27693,6 @@
       <c r="B1521" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1521" s="4" t="n"/>
       <c r="D1521" s="4" t="n"/>
       <c r="E1521" s="4" t="n"/>
       <c r="F1521" s="4" t="n"/>
@@ -27692,6 +27704,7 @@
       <c r="L1521" s="4" t="n"/>
       <c r="M1521" s="4" t="n"/>
       <c r="N1521" s="4" t="n"/>
+      <c r="O1521" s="4" t="n"/>
     </row>
     <row r="1522">
       <c r="A1522" s="5" t="n">
@@ -27700,7 +27713,6 @@
       <c r="B1522" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1522" s="4" t="n"/>
       <c r="D1522" s="4" t="n"/>
       <c r="E1522" s="4" t="n"/>
       <c r="F1522" s="4" t="n"/>
@@ -27712,6 +27724,7 @@
       <c r="L1522" s="4" t="n"/>
       <c r="M1522" s="4" t="n"/>
       <c r="N1522" s="4" t="n"/>
+      <c r="O1522" s="4" t="n"/>
     </row>
     <row r="1523">
       <c r="A1523" s="5" t="n">
@@ -27720,7 +27733,6 @@
       <c r="B1523" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1523" s="4" t="n"/>
       <c r="D1523" s="4" t="n"/>
       <c r="E1523" s="4" t="n"/>
       <c r="F1523" s="4" t="n"/>
@@ -27732,6 +27744,7 @@
       <c r="L1523" s="4" t="n"/>
       <c r="M1523" s="4" t="n"/>
       <c r="N1523" s="4" t="n"/>
+      <c r="O1523" s="4" t="n"/>
     </row>
     <row r="1524">
       <c r="A1524" s="6" t="n">
@@ -27740,7 +27753,6 @@
       <c r="B1524" s="7" t="n">
         <v>-65</v>
       </c>
-      <c r="C1524" s="7" t="n"/>
       <c r="D1524" s="7" t="n"/>
       <c r="E1524" s="7" t="n"/>
       <c r="F1524" s="7" t="n"/>
@@ -27752,6 +27764,7 @@
       <c r="L1524" s="7" t="n"/>
       <c r="M1524" s="7" t="n"/>
       <c r="N1524" s="7" t="n"/>
+      <c r="O1524" s="7" t="n"/>
     </row>
     <row r="1525">
       <c r="A1525" s="5" t="n">
@@ -27760,7 +27773,6 @@
       <c r="B1525" s="3" t="n">
         <v>-6.5</v>
       </c>
-      <c r="C1525" s="4" t="n"/>
       <c r="D1525" s="4" t="n"/>
       <c r="E1525" s="4" t="n"/>
       <c r="F1525" s="4" t="n"/>
@@ -27772,6 +27784,7 @@
       <c r="L1525" s="4" t="n"/>
       <c r="M1525" s="4" t="n"/>
       <c r="N1525" s="4" t="n"/>
+      <c r="O1525" s="4" t="n"/>
     </row>
     <row r="1526">
       <c r="A1526" s="5" t="n">
@@ -27780,7 +27793,6 @@
       <c r="B1526" s="3" t="n">
         <v>-6.5</v>
       </c>
-      <c r="C1526" s="4" t="n"/>
       <c r="D1526" s="4" t="n"/>
       <c r="E1526" s="4" t="n"/>
       <c r="F1526" s="4" t="n"/>
@@ -27792,6 +27804,7 @@
       <c r="L1526" s="4" t="n"/>
       <c r="M1526" s="4" t="n"/>
       <c r="N1526" s="4" t="n"/>
+      <c r="O1526" s="4" t="n"/>
     </row>
     <row r="1527">
       <c r="A1527" s="5" t="n">
@@ -27800,7 +27813,6 @@
       <c r="B1527" s="3" t="n">
         <v>-60</v>
       </c>
-      <c r="C1527" s="4" t="n"/>
       <c r="D1527" s="4" t="n"/>
       <c r="E1527" s="4" t="n"/>
       <c r="F1527" s="4" t="n"/>
@@ -27812,6 +27824,7 @@
       <c r="L1527" s="4" t="n"/>
       <c r="M1527" s="4" t="n"/>
       <c r="N1527" s="4" t="n"/>
+      <c r="O1527" s="4" t="n"/>
     </row>
     <row r="1528">
       <c r="A1528" s="5" t="n">
@@ -27820,7 +27833,6 @@
       <c r="B1528" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1528" s="4" t="n"/>
       <c r="D1528" s="4" t="n"/>
       <c r="E1528" s="4" t="n"/>
       <c r="F1528" s="4" t="n"/>
@@ -27832,6 +27844,7 @@
       <c r="L1528" s="4" t="n"/>
       <c r="M1528" s="4" t="n"/>
       <c r="N1528" s="4" t="n"/>
+      <c r="O1528" s="4" t="n"/>
     </row>
     <row r="1529">
       <c r="A1529" s="5" t="n">
@@ -27840,7 +27853,6 @@
       <c r="B1529" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1529" s="4" t="n"/>
       <c r="D1529" s="4" t="n"/>
       <c r="E1529" s="4" t="n"/>
       <c r="F1529" s="4" t="n"/>
@@ -27852,6 +27864,7 @@
       <c r="L1529" s="4" t="n"/>
       <c r="M1529" s="4" t="n"/>
       <c r="N1529" s="4" t="n"/>
+      <c r="O1529" s="4" t="n"/>
     </row>
     <row r="1530">
       <c r="A1530" s="5" t="n">
@@ -27860,7 +27873,6 @@
       <c r="B1530" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1530" s="4" t="n"/>
       <c r="D1530" s="4" t="n"/>
       <c r="E1530" s="4" t="n"/>
       <c r="F1530" s="4" t="n"/>
@@ -27872,6 +27884,7 @@
       <c r="L1530" s="4" t="n"/>
       <c r="M1530" s="4" t="n"/>
       <c r="N1530" s="4" t="n"/>
+      <c r="O1530" s="4" t="n"/>
     </row>
     <row r="1531">
       <c r="A1531" s="5" t="n">
@@ -27880,7 +27893,6 @@
       <c r="B1531" s="3" t="n">
         <v>-60</v>
       </c>
-      <c r="C1531" s="4" t="n"/>
       <c r="D1531" s="4" t="n"/>
       <c r="E1531" s="4" t="n"/>
       <c r="F1531" s="4" t="n"/>
@@ -27892,6 +27904,7 @@
       <c r="L1531" s="4" t="n"/>
       <c r="M1531" s="4" t="n"/>
       <c r="N1531" s="4" t="n"/>
+      <c r="O1531" s="4" t="n"/>
     </row>
     <row r="1532">
       <c r="A1532" s="5" t="n">
@@ -27900,7 +27913,6 @@
       <c r="B1532" s="3" t="n">
         <v>-60</v>
       </c>
-      <c r="C1532" s="4" t="n"/>
       <c r="D1532" s="4" t="n"/>
       <c r="E1532" s="4" t="n"/>
       <c r="F1532" s="4" t="n"/>
@@ -27912,6 +27924,7 @@
       <c r="L1532" s="4" t="n"/>
       <c r="M1532" s="4" t="n"/>
       <c r="N1532" s="4" t="n"/>
+      <c r="O1532" s="4" t="n"/>
     </row>
     <row r="1533">
       <c r="A1533" s="5" t="n">
@@ -27920,7 +27933,6 @@
       <c r="B1533" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1533" s="4" t="n"/>
       <c r="D1533" s="4" t="n"/>
       <c r="E1533" s="4" t="n"/>
       <c r="F1533" s="4" t="n"/>
@@ -27932,6 +27944,7 @@
       <c r="L1533" s="4" t="n"/>
       <c r="M1533" s="4" t="n"/>
       <c r="N1533" s="4" t="n"/>
+      <c r="O1533" s="4" t="n"/>
     </row>
     <row r="1534">
       <c r="A1534" s="6" t="n">
@@ -27940,7 +27953,6 @@
       <c r="B1534" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1534" s="7" t="n"/>
       <c r="D1534" s="7" t="n"/>
       <c r="E1534" s="7" t="n"/>
       <c r="F1534" s="7" t="n"/>
@@ -27952,6 +27964,7 @@
       <c r="L1534" s="7" t="n"/>
       <c r="M1534" s="7" t="n"/>
       <c r="N1534" s="7" t="n"/>
+      <c r="O1534" s="7" t="n"/>
     </row>
     <row r="1535">
       <c r="A1535" s="5" t="n">
@@ -27960,7 +27973,6 @@
       <c r="B1535" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1535" s="4" t="n"/>
       <c r="D1535" s="4" t="n"/>
       <c r="E1535" s="4" t="n"/>
       <c r="F1535" s="4" t="n"/>
@@ -27972,13 +27984,17 @@
       <c r="L1535" s="4" t="n"/>
       <c r="M1535" s="4" t="n"/>
       <c r="N1535" s="4" t="n"/>
+      <c r="O1535" s="4" t="n"/>
     </row>
     <row r="1536">
       <c r="A1536" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B1536" t="n">
-        <v>-67.5</v>
+        <v>-57.5</v>
+      </c>
+      <c r="C1536" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27992,7 +28008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1518"/>
+  <dimension ref="A1:O1518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28006,62 +28022,67 @@
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jan_Delivery</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Feb_Delivery</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mar_Delivery</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apr_Delivery</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>May_Delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jun_Delivery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jul_Delivery</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Aug_Delivery</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sep_Delivery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Oct_Delivery</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nov_Delivery</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Dec_Delivery</t>
         </is>
@@ -39698,7 +39719,6 @@
       <c r="B1455" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1455" s="7" t="n"/>
       <c r="D1455" s="7" t="n"/>
       <c r="E1455" s="7" t="n"/>
       <c r="F1455" s="7" t="n"/>
@@ -39710,6 +39730,7 @@
       <c r="L1455" s="7" t="n"/>
       <c r="M1455" s="7" t="n"/>
       <c r="N1455" s="7" t="n"/>
+      <c r="O1455" s="7" t="n"/>
     </row>
     <row r="1456">
       <c r="A1456" s="6" t="n">
@@ -39718,7 +39739,6 @@
       <c r="B1456" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1456" s="7" t="n"/>
       <c r="D1456" s="7" t="n"/>
       <c r="E1456" s="7" t="n"/>
       <c r="F1456" s="7" t="n"/>
@@ -39730,6 +39750,7 @@
       <c r="L1456" s="7" t="n"/>
       <c r="M1456" s="7" t="n"/>
       <c r="N1456" s="7" t="n"/>
+      <c r="O1456" s="7" t="n"/>
     </row>
     <row r="1457">
       <c r="A1457" s="6" t="n">
@@ -39738,7 +39759,6 @@
       <c r="B1457" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1457" s="7" t="n"/>
       <c r="D1457" s="7" t="n"/>
       <c r="E1457" s="7" t="n"/>
       <c r="F1457" s="7" t="n"/>
@@ -39750,6 +39770,7 @@
       <c r="L1457" s="7" t="n"/>
       <c r="M1457" s="7" t="n"/>
       <c r="N1457" s="7" t="n"/>
+      <c r="O1457" s="7" t="n"/>
     </row>
     <row r="1458">
       <c r="A1458" s="6" t="n">
@@ -39758,7 +39779,6 @@
       <c r="B1458" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1458" s="7" t="n"/>
       <c r="D1458" s="7" t="n"/>
       <c r="E1458" s="7" t="n"/>
       <c r="F1458" s="7" t="n"/>
@@ -39770,6 +39790,7 @@
       <c r="L1458" s="7" t="n"/>
       <c r="M1458" s="7" t="n"/>
       <c r="N1458" s="7" t="n"/>
+      <c r="O1458" s="7" t="n"/>
     </row>
     <row r="1459">
       <c r="A1459" s="6" t="n">
@@ -39778,7 +39799,6 @@
       <c r="B1459" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1459" s="7" t="n"/>
       <c r="D1459" s="7" t="n"/>
       <c r="E1459" s="7" t="n"/>
       <c r="F1459" s="7" t="n"/>
@@ -39790,6 +39810,7 @@
       <c r="L1459" s="7" t="n"/>
       <c r="M1459" s="7" t="n"/>
       <c r="N1459" s="7" t="n"/>
+      <c r="O1459" s="7" t="n"/>
     </row>
     <row r="1460">
       <c r="A1460" s="6" t="n">
@@ -39798,7 +39819,6 @@
       <c r="B1460" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1460" s="7" t="n"/>
       <c r="D1460" s="7" t="n"/>
       <c r="E1460" s="7" t="n"/>
       <c r="F1460" s="7" t="n"/>
@@ -39810,6 +39830,7 @@
       <c r="L1460" s="7" t="n"/>
       <c r="M1460" s="7" t="n"/>
       <c r="N1460" s="7" t="n"/>
+      <c r="O1460" s="7" t="n"/>
     </row>
     <row r="1461">
       <c r="A1461" s="6" t="n">
@@ -39818,7 +39839,6 @@
       <c r="B1461" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1461" s="7" t="n"/>
       <c r="D1461" s="7" t="n"/>
       <c r="E1461" s="7" t="n"/>
       <c r="F1461" s="7" t="n"/>
@@ -39830,6 +39850,7 @@
       <c r="L1461" s="7" t="n"/>
       <c r="M1461" s="7" t="n"/>
       <c r="N1461" s="7" t="n"/>
+      <c r="O1461" s="7" t="n"/>
     </row>
     <row r="1462">
       <c r="A1462" s="6" t="n">
@@ -39838,7 +39859,6 @@
       <c r="B1462" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1462" s="7" t="n"/>
       <c r="D1462" s="7" t="n"/>
       <c r="E1462" s="7" t="n"/>
       <c r="F1462" s="7" t="n"/>
@@ -39850,6 +39870,7 @@
       <c r="L1462" s="7" t="n"/>
       <c r="M1462" s="7" t="n"/>
       <c r="N1462" s="7" t="n"/>
+      <c r="O1462" s="7" t="n"/>
     </row>
     <row r="1463">
       <c r="A1463" s="6" t="n">
@@ -39858,7 +39879,6 @@
       <c r="B1463" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1463" s="7" t="n"/>
       <c r="D1463" s="7" t="n"/>
       <c r="E1463" s="7" t="n"/>
       <c r="F1463" s="7" t="n"/>
@@ -39870,6 +39890,7 @@
       <c r="L1463" s="7" t="n"/>
       <c r="M1463" s="7" t="n"/>
       <c r="N1463" s="7" t="n"/>
+      <c r="O1463" s="7" t="n"/>
     </row>
     <row r="1464">
       <c r="A1464" s="5" t="n">
@@ -39878,7 +39899,6 @@
       <c r="B1464" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1464" s="4" t="n"/>
       <c r="D1464" s="4" t="n"/>
       <c r="E1464" s="4" t="n"/>
       <c r="F1464" s="4" t="n"/>
@@ -39890,6 +39910,7 @@
       <c r="L1464" s="4" t="n"/>
       <c r="M1464" s="4" t="n"/>
       <c r="N1464" s="4" t="n"/>
+      <c r="O1464" s="4" t="n"/>
     </row>
     <row r="1465">
       <c r="A1465" s="5" t="n">
@@ -39898,7 +39919,6 @@
       <c r="B1465" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1465" s="4" t="n"/>
       <c r="D1465" s="4" t="n"/>
       <c r="E1465" s="4" t="n"/>
       <c r="F1465" s="4" t="n"/>
@@ -39910,6 +39930,7 @@
       <c r="L1465" s="4" t="n"/>
       <c r="M1465" s="4" t="n"/>
       <c r="N1465" s="4" t="n"/>
+      <c r="O1465" s="4" t="n"/>
     </row>
     <row r="1466">
       <c r="A1466" s="5" t="n">
@@ -39918,7 +39939,6 @@
       <c r="B1466" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1466" s="4" t="n"/>
       <c r="D1466" s="4" t="n"/>
       <c r="E1466" s="4" t="n"/>
       <c r="F1466" s="4" t="n"/>
@@ -39930,6 +39950,7 @@
       <c r="L1466" s="4" t="n"/>
       <c r="M1466" s="4" t="n"/>
       <c r="N1466" s="4" t="n"/>
+      <c r="O1466" s="4" t="n"/>
     </row>
     <row r="1467">
       <c r="A1467" s="5" t="n">
@@ -39938,7 +39959,6 @@
       <c r="B1467" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1467" s="4" t="n"/>
       <c r="D1467" s="4" t="n"/>
       <c r="E1467" s="4" t="n"/>
       <c r="F1467" s="4" t="n"/>
@@ -39950,6 +39970,7 @@
       <c r="L1467" s="4" t="n"/>
       <c r="M1467" s="4" t="n"/>
       <c r="N1467" s="4" t="n"/>
+      <c r="O1467" s="4" t="n"/>
     </row>
     <row r="1468">
       <c r="A1468" s="5" t="n">
@@ -39958,7 +39979,6 @@
       <c r="B1468" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1468" s="4" t="n"/>
       <c r="D1468" s="4" t="n"/>
       <c r="E1468" s="4" t="n"/>
       <c r="F1468" s="4" t="n"/>
@@ -39970,6 +39990,7 @@
       <c r="L1468" s="4" t="n"/>
       <c r="M1468" s="4" t="n"/>
       <c r="N1468" s="4" t="n"/>
+      <c r="O1468" s="4" t="n"/>
     </row>
     <row r="1469">
       <c r="A1469" s="5" t="n">
@@ -39978,7 +39999,6 @@
       <c r="B1469" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1469" s="4" t="n"/>
       <c r="D1469" s="4" t="n"/>
       <c r="E1469" s="4" t="n"/>
       <c r="F1469" s="4" t="n"/>
@@ -39990,6 +40010,7 @@
       <c r="L1469" s="4" t="n"/>
       <c r="M1469" s="4" t="n"/>
       <c r="N1469" s="4" t="n"/>
+      <c r="O1469" s="4" t="n"/>
     </row>
     <row r="1470">
       <c r="A1470" s="5" t="n">
@@ -39998,7 +40019,6 @@
       <c r="B1470" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1470" s="4" t="n"/>
       <c r="D1470" s="4" t="n"/>
       <c r="E1470" s="4" t="n"/>
       <c r="F1470" s="4" t="n"/>
@@ -40010,6 +40030,7 @@
       <c r="L1470" s="4" t="n"/>
       <c r="M1470" s="4" t="n"/>
       <c r="N1470" s="4" t="n"/>
+      <c r="O1470" s="4" t="n"/>
     </row>
     <row r="1471">
       <c r="A1471" s="5" t="n">
@@ -40018,7 +40039,6 @@
       <c r="B1471" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1471" s="4" t="n"/>
       <c r="D1471" s="4" t="n"/>
       <c r="E1471" s="4" t="n"/>
       <c r="F1471" s="4" t="n"/>
@@ -40030,6 +40050,7 @@
       <c r="L1471" s="4" t="n"/>
       <c r="M1471" s="4" t="n"/>
       <c r="N1471" s="4" t="n"/>
+      <c r="O1471" s="4" t="n"/>
     </row>
     <row r="1472">
       <c r="A1472" s="5" t="n">
@@ -40038,7 +40059,6 @@
       <c r="B1472" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1472" s="4" t="n"/>
       <c r="D1472" s="4" t="n"/>
       <c r="E1472" s="4" t="n"/>
       <c r="F1472" s="4" t="n"/>
@@ -40050,6 +40070,7 @@
       <c r="L1472" s="4" t="n"/>
       <c r="M1472" s="4" t="n"/>
       <c r="N1472" s="4" t="n"/>
+      <c r="O1472" s="4" t="n"/>
     </row>
     <row r="1473">
       <c r="A1473" s="5" t="n">
@@ -40058,7 +40079,6 @@
       <c r="B1473" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1473" s="4" t="n"/>
       <c r="D1473" s="4" t="n"/>
       <c r="E1473" s="4" t="n"/>
       <c r="F1473" s="4" t="n"/>
@@ -40070,6 +40090,7 @@
       <c r="L1473" s="4" t="n"/>
       <c r="M1473" s="4" t="n"/>
       <c r="N1473" s="4" t="n"/>
+      <c r="O1473" s="4" t="n"/>
     </row>
     <row r="1474">
       <c r="A1474" s="5" t="n">
@@ -40078,7 +40099,6 @@
       <c r="B1474" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1474" s="4" t="n"/>
       <c r="D1474" s="4" t="n"/>
       <c r="E1474" s="4" t="n"/>
       <c r="F1474" s="4" t="n"/>
@@ -40090,6 +40110,7 @@
       <c r="L1474" s="4" t="n"/>
       <c r="M1474" s="4" t="n"/>
       <c r="N1474" s="4" t="n"/>
+      <c r="O1474" s="4" t="n"/>
     </row>
     <row r="1475">
       <c r="A1475" s="5" t="n">
@@ -40098,7 +40119,6 @@
       <c r="B1475" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1475" s="4" t="n"/>
       <c r="D1475" s="4" t="n"/>
       <c r="E1475" s="4" t="n"/>
       <c r="F1475" s="4" t="n"/>
@@ -40110,6 +40130,7 @@
       <c r="L1475" s="4" t="n"/>
       <c r="M1475" s="4" t="n"/>
       <c r="N1475" s="4" t="n"/>
+      <c r="O1475" s="4" t="n"/>
     </row>
     <row r="1476">
       <c r="A1476" s="5" t="n">
@@ -40118,7 +40139,6 @@
       <c r="B1476" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1476" s="4" t="n"/>
       <c r="D1476" s="4" t="n"/>
       <c r="E1476" s="4" t="n"/>
       <c r="F1476" s="4" t="n"/>
@@ -40130,6 +40150,7 @@
       <c r="L1476" s="4" t="n"/>
       <c r="M1476" s="4" t="n"/>
       <c r="N1476" s="4" t="n"/>
+      <c r="O1476" s="4" t="n"/>
     </row>
     <row r="1477">
       <c r="A1477" s="5" t="n">
@@ -40138,7 +40159,6 @@
       <c r="B1477" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1477" s="4" t="n"/>
       <c r="D1477" s="4" t="n"/>
       <c r="E1477" s="4" t="n"/>
       <c r="F1477" s="4" t="n"/>
@@ -40150,6 +40170,7 @@
       <c r="L1477" s="4" t="n"/>
       <c r="M1477" s="4" t="n"/>
       <c r="N1477" s="4" t="n"/>
+      <c r="O1477" s="4" t="n"/>
     </row>
     <row r="1478">
       <c r="A1478" s="5" t="n">
@@ -40158,7 +40179,6 @@
       <c r="B1478" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1478" s="4" t="n"/>
       <c r="D1478" s="4" t="n"/>
       <c r="E1478" s="4" t="n"/>
       <c r="F1478" s="4" t="n"/>
@@ -40170,6 +40190,7 @@
       <c r="L1478" s="4" t="n"/>
       <c r="M1478" s="4" t="n"/>
       <c r="N1478" s="4" t="n"/>
+      <c r="O1478" s="4" t="n"/>
     </row>
     <row r="1479">
       <c r="A1479" s="5" t="n">
@@ -40178,7 +40199,6 @@
       <c r="B1479" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1479" s="4" t="n"/>
       <c r="D1479" s="4" t="n"/>
       <c r="E1479" s="4" t="n"/>
       <c r="F1479" s="4" t="n"/>
@@ -40190,6 +40210,7 @@
       <c r="L1479" s="4" t="n"/>
       <c r="M1479" s="4" t="n"/>
       <c r="N1479" s="4" t="n"/>
+      <c r="O1479" s="4" t="n"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6" t="n">
@@ -40198,7 +40219,6 @@
       <c r="B1480" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1480" s="7" t="n"/>
       <c r="D1480" s="7" t="n"/>
       <c r="E1480" s="7" t="n"/>
       <c r="F1480" s="7" t="n"/>
@@ -40210,6 +40230,7 @@
       <c r="L1480" s="7" t="n"/>
       <c r="M1480" s="7" t="n"/>
       <c r="N1480" s="7" t="n"/>
+      <c r="O1480" s="7" t="n"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6" t="n">
@@ -40218,7 +40239,6 @@
       <c r="B1481" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1481" s="7" t="n"/>
       <c r="D1481" s="7" t="n"/>
       <c r="E1481" s="7" t="n"/>
       <c r="F1481" s="7" t="n"/>
@@ -40230,6 +40250,7 @@
       <c r="L1481" s="7" t="n"/>
       <c r="M1481" s="7" t="n"/>
       <c r="N1481" s="7" t="n"/>
+      <c r="O1481" s="7" t="n"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6" t="n">
@@ -40238,7 +40259,6 @@
       <c r="B1482" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1482" s="7" t="n"/>
       <c r="D1482" s="7" t="n"/>
       <c r="E1482" s="7" t="n"/>
       <c r="F1482" s="7" t="n"/>
@@ -40250,6 +40270,7 @@
       <c r="L1482" s="7" t="n"/>
       <c r="M1482" s="7" t="n"/>
       <c r="N1482" s="7" t="n"/>
+      <c r="O1482" s="7" t="n"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6" t="n">
@@ -40258,7 +40279,6 @@
       <c r="B1483" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1483" s="7" t="n"/>
       <c r="D1483" s="7" t="n"/>
       <c r="E1483" s="7" t="n"/>
       <c r="F1483" s="7" t="n"/>
@@ -40270,6 +40290,7 @@
       <c r="L1483" s="7" t="n"/>
       <c r="M1483" s="7" t="n"/>
       <c r="N1483" s="7" t="n"/>
+      <c r="O1483" s="7" t="n"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6" t="n">
@@ -40278,7 +40299,6 @@
       <c r="B1484" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1484" s="7" t="n"/>
       <c r="D1484" s="7" t="n"/>
       <c r="E1484" s="7" t="n"/>
       <c r="F1484" s="7" t="n"/>
@@ -40290,6 +40310,7 @@
       <c r="L1484" s="7" t="n"/>
       <c r="M1484" s="7" t="n"/>
       <c r="N1484" s="7" t="n"/>
+      <c r="O1484" s="7" t="n"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6" t="n">
@@ -40298,7 +40319,6 @@
       <c r="B1485" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1485" s="7" t="n"/>
       <c r="D1485" s="7" t="n"/>
       <c r="E1485" s="7" t="n"/>
       <c r="F1485" s="7" t="n"/>
@@ -40310,6 +40330,7 @@
       <c r="L1485" s="7" t="n"/>
       <c r="M1485" s="7" t="n"/>
       <c r="N1485" s="7" t="n"/>
+      <c r="O1485" s="7" t="n"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6" t="n">
@@ -40318,7 +40339,6 @@
       <c r="B1486" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1486" s="7" t="n"/>
       <c r="D1486" s="7" t="n"/>
       <c r="E1486" s="7" t="n"/>
       <c r="F1486" s="7" t="n"/>
@@ -40330,6 +40350,7 @@
       <c r="L1486" s="7" t="n"/>
       <c r="M1486" s="7" t="n"/>
       <c r="N1486" s="7" t="n"/>
+      <c r="O1486" s="7" t="n"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6" t="n">
@@ -40338,7 +40359,6 @@
       <c r="B1487" s="7" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1487" s="7" t="n"/>
       <c r="D1487" s="7" t="n"/>
       <c r="E1487" s="7" t="n"/>
       <c r="F1487" s="7" t="n"/>
@@ -40350,6 +40370,7 @@
       <c r="L1487" s="7" t="n"/>
       <c r="M1487" s="7" t="n"/>
       <c r="N1487" s="7" t="n"/>
+      <c r="O1487" s="7" t="n"/>
     </row>
     <row r="1488">
       <c r="A1488" s="5" t="n">
@@ -40358,7 +40379,6 @@
       <c r="B1488" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1488" s="4" t="n"/>
       <c r="D1488" s="4" t="n"/>
       <c r="E1488" s="4" t="n"/>
       <c r="F1488" s="4" t="n"/>
@@ -40370,6 +40390,7 @@
       <c r="L1488" s="4" t="n"/>
       <c r="M1488" s="4" t="n"/>
       <c r="N1488" s="4" t="n"/>
+      <c r="O1488" s="4" t="n"/>
     </row>
     <row r="1489">
       <c r="A1489" s="5" t="n">
@@ -40378,7 +40399,6 @@
       <c r="B1489" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1489" s="4" t="n"/>
       <c r="D1489" s="4" t="n"/>
       <c r="E1489" s="4" t="n"/>
       <c r="F1489" s="4" t="n"/>
@@ -40390,6 +40410,7 @@
       <c r="L1489" s="4" t="n"/>
       <c r="M1489" s="4" t="n"/>
       <c r="N1489" s="4" t="n"/>
+      <c r="O1489" s="4" t="n"/>
     </row>
     <row r="1490">
       <c r="A1490" s="5" t="n">
@@ -40398,7 +40419,6 @@
       <c r="B1490" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1490" s="4" t="n"/>
       <c r="D1490" s="4" t="n"/>
       <c r="E1490" s="4" t="n"/>
       <c r="F1490" s="4" t="n"/>
@@ -40410,6 +40430,7 @@
       <c r="L1490" s="4" t="n"/>
       <c r="M1490" s="4" t="n"/>
       <c r="N1490" s="4" t="n"/>
+      <c r="O1490" s="4" t="n"/>
     </row>
     <row r="1491">
       <c r="A1491" s="5" t="n">
@@ -40418,7 +40439,6 @@
       <c r="B1491" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1491" s="4" t="n"/>
       <c r="D1491" s="4" t="n"/>
       <c r="E1491" s="4" t="n"/>
       <c r="F1491" s="4" t="n"/>
@@ -40430,6 +40450,7 @@
       <c r="L1491" s="4" t="n"/>
       <c r="M1491" s="4" t="n"/>
       <c r="N1491" s="4" t="n"/>
+      <c r="O1491" s="4" t="n"/>
     </row>
     <row r="1492">
       <c r="A1492" s="5" t="n">
@@ -40438,7 +40459,6 @@
       <c r="B1492" s="3" t="n">
         <v>-57.5</v>
       </c>
-      <c r="C1492" s="4" t="n"/>
       <c r="D1492" s="4" t="n"/>
       <c r="E1492" s="4" t="n"/>
       <c r="F1492" s="4" t="n"/>
@@ -40450,6 +40470,7 @@
       <c r="L1492" s="4" t="n"/>
       <c r="M1492" s="4" t="n"/>
       <c r="N1492" s="4" t="n"/>
+      <c r="O1492" s="4" t="n"/>
     </row>
     <row r="1493">
       <c r="A1493" s="5" t="n">
@@ -40458,7 +40479,6 @@
       <c r="B1493" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1493" s="4" t="n"/>
       <c r="D1493" s="4" t="n"/>
       <c r="E1493" s="4" t="n"/>
       <c r="F1493" s="4" t="n"/>
@@ -40470,6 +40490,7 @@
       <c r="L1493" s="4" t="n"/>
       <c r="M1493" s="4" t="n"/>
       <c r="N1493" s="4" t="n"/>
+      <c r="O1493" s="4" t="n"/>
     </row>
     <row r="1494">
       <c r="A1494" s="5" t="n">
@@ -40478,7 +40499,6 @@
       <c r="B1494" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1494" s="4" t="n"/>
       <c r="D1494" s="4" t="n"/>
       <c r="E1494" s="4" t="n"/>
       <c r="F1494" s="4" t="n"/>
@@ -40490,6 +40510,7 @@
       <c r="L1494" s="4" t="n"/>
       <c r="M1494" s="4" t="n"/>
       <c r="N1494" s="4" t="n"/>
+      <c r="O1494" s="4" t="n"/>
     </row>
     <row r="1495">
       <c r="A1495" s="5" t="n">
@@ -40498,7 +40519,6 @@
       <c r="B1495" s="3" t="n">
         <v>-65</v>
       </c>
-      <c r="C1495" s="4" t="n"/>
       <c r="D1495" s="4" t="n"/>
       <c r="E1495" s="4" t="n"/>
       <c r="F1495" s="4" t="n"/>
@@ -40510,6 +40530,7 @@
       <c r="L1495" s="4" t="n"/>
       <c r="M1495" s="4" t="n"/>
       <c r="N1495" s="4" t="n"/>
+      <c r="O1495" s="4" t="n"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6" t="n">
@@ -40518,7 +40539,6 @@
       <c r="B1496" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1496" s="7" t="n"/>
       <c r="D1496" s="7" t="n"/>
       <c r="E1496" s="7" t="n"/>
       <c r="F1496" s="7" t="n"/>
@@ -40530,6 +40550,7 @@
       <c r="L1496" s="7" t="n"/>
       <c r="M1496" s="7" t="n"/>
       <c r="N1496" s="7" t="n"/>
+      <c r="O1496" s="7" t="n"/>
     </row>
     <row r="1497">
       <c r="A1497" s="6" t="n">
@@ -40538,7 +40559,6 @@
       <c r="B1497" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1497" s="7" t="n"/>
       <c r="D1497" s="7" t="n"/>
       <c r="E1497" s="7" t="n"/>
       <c r="F1497" s="7" t="n"/>
@@ -40550,6 +40570,7 @@
       <c r="L1497" s="7" t="n"/>
       <c r="M1497" s="7" t="n"/>
       <c r="N1497" s="7" t="n"/>
+      <c r="O1497" s="7" t="n"/>
     </row>
     <row r="1498">
       <c r="A1498" s="5" t="n">
@@ -40558,7 +40579,6 @@
       <c r="B1498" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1498" s="4" t="n"/>
       <c r="D1498" s="4" t="n"/>
       <c r="E1498" s="4" t="n"/>
       <c r="F1498" s="4" t="n"/>
@@ -40570,6 +40590,7 @@
       <c r="L1498" s="4" t="n"/>
       <c r="M1498" s="4" t="n"/>
       <c r="N1498" s="4" t="n"/>
+      <c r="O1498" s="4" t="n"/>
     </row>
     <row r="1499">
       <c r="A1499" s="5" t="n">
@@ -40578,7 +40599,6 @@
       <c r="B1499" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1499" s="4" t="n"/>
       <c r="D1499" s="4" t="n"/>
       <c r="E1499" s="4" t="n"/>
       <c r="F1499" s="4" t="n"/>
@@ -40590,6 +40610,7 @@
       <c r="L1499" s="4" t="n"/>
       <c r="M1499" s="4" t="n"/>
       <c r="N1499" s="4" t="n"/>
+      <c r="O1499" s="4" t="n"/>
     </row>
     <row r="1500">
       <c r="A1500" s="5" t="n">
@@ -40598,7 +40619,6 @@
       <c r="B1500" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1500" s="4" t="n"/>
       <c r="D1500" s="4" t="n"/>
       <c r="E1500" s="4" t="n"/>
       <c r="F1500" s="4" t="n"/>
@@ -40610,6 +40630,7 @@
       <c r="L1500" s="4" t="n"/>
       <c r="M1500" s="4" t="n"/>
       <c r="N1500" s="4" t="n"/>
+      <c r="O1500" s="4" t="n"/>
     </row>
     <row r="1501">
       <c r="A1501" s="5" t="n">
@@ -40618,7 +40639,6 @@
       <c r="B1501" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1501" s="4" t="n"/>
       <c r="D1501" s="4" t="n"/>
       <c r="E1501" s="4" t="n"/>
       <c r="F1501" s="4" t="n"/>
@@ -40630,6 +40650,7 @@
       <c r="L1501" s="4" t="n"/>
       <c r="M1501" s="4" t="n"/>
       <c r="N1501" s="4" t="n"/>
+      <c r="O1501" s="4" t="n"/>
     </row>
     <row r="1502">
       <c r="A1502" s="6" t="n">
@@ -40638,7 +40659,6 @@
       <c r="B1502" s="7" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1502" s="7" t="n"/>
       <c r="D1502" s="7" t="n"/>
       <c r="E1502" s="7" t="n"/>
       <c r="F1502" s="7" t="n"/>
@@ -40650,6 +40670,7 @@
       <c r="L1502" s="7" t="n"/>
       <c r="M1502" s="7" t="n"/>
       <c r="N1502" s="7" t="n"/>
+      <c r="O1502" s="7" t="n"/>
     </row>
     <row r="1503">
       <c r="A1503" s="5" t="n">
@@ -40658,7 +40679,6 @@
       <c r="B1503" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1503" s="4" t="n"/>
       <c r="D1503" s="4" t="n"/>
       <c r="E1503" s="4" t="n"/>
       <c r="F1503" s="4" t="n"/>
@@ -40670,6 +40690,7 @@
       <c r="L1503" s="4" t="n"/>
       <c r="M1503" s="4" t="n"/>
       <c r="N1503" s="4" t="n"/>
+      <c r="O1503" s="4" t="n"/>
     </row>
     <row r="1504">
       <c r="A1504" s="5" t="n">
@@ -40678,7 +40699,6 @@
       <c r="B1504" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1504" s="4" t="n"/>
       <c r="D1504" s="4" t="n"/>
       <c r="E1504" s="4" t="n"/>
       <c r="F1504" s="4" t="n"/>
@@ -40690,6 +40710,7 @@
       <c r="L1504" s="4" t="n"/>
       <c r="M1504" s="4" t="n"/>
       <c r="N1504" s="4" t="n"/>
+      <c r="O1504" s="4" t="n"/>
     </row>
     <row r="1505">
       <c r="A1505" s="5" t="n">
@@ -40698,7 +40719,6 @@
       <c r="B1505" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1505" s="4" t="n"/>
       <c r="D1505" s="4" t="n"/>
       <c r="E1505" s="4" t="n"/>
       <c r="F1505" s="4" t="n"/>
@@ -40710,6 +40730,7 @@
       <c r="L1505" s="4" t="n"/>
       <c r="M1505" s="4" t="n"/>
       <c r="N1505" s="4" t="n"/>
+      <c r="O1505" s="4" t="n"/>
     </row>
     <row r="1506">
       <c r="A1506" s="6" t="n">
@@ -40718,7 +40739,6 @@
       <c r="B1506" s="7" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1506" s="7" t="n"/>
       <c r="D1506" s="7" t="n"/>
       <c r="E1506" s="7" t="n"/>
       <c r="F1506" s="7" t="n"/>
@@ -40730,6 +40750,7 @@
       <c r="L1506" s="7" t="n"/>
       <c r="M1506" s="7" t="n"/>
       <c r="N1506" s="7" t="n"/>
+      <c r="O1506" s="7" t="n"/>
     </row>
     <row r="1507">
       <c r="A1507" s="5" t="n">
@@ -40738,7 +40759,6 @@
       <c r="B1507" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1507" s="4" t="n"/>
       <c r="D1507" s="4" t="n"/>
       <c r="E1507" s="4" t="n"/>
       <c r="F1507" s="4" t="n"/>
@@ -40750,6 +40770,7 @@
       <c r="L1507" s="4" t="n"/>
       <c r="M1507" s="4" t="n"/>
       <c r="N1507" s="4" t="n"/>
+      <c r="O1507" s="4" t="n"/>
     </row>
     <row r="1508">
       <c r="A1508" s="5" t="n">
@@ -40758,7 +40779,6 @@
       <c r="B1508" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1508" s="4" t="n"/>
       <c r="D1508" s="4" t="n"/>
       <c r="E1508" s="4" t="n"/>
       <c r="F1508" s="4" t="n"/>
@@ -40770,6 +40790,7 @@
       <c r="L1508" s="4" t="n"/>
       <c r="M1508" s="4" t="n"/>
       <c r="N1508" s="4" t="n"/>
+      <c r="O1508" s="4" t="n"/>
     </row>
     <row r="1509">
       <c r="A1509" s="5" t="n">
@@ -40778,7 +40799,6 @@
       <c r="B1509" s="3" t="n">
         <v>-62.5</v>
       </c>
-      <c r="C1509" s="4" t="n"/>
       <c r="D1509" s="4" t="n"/>
       <c r="E1509" s="4" t="n"/>
       <c r="F1509" s="4" t="n"/>
@@ -40790,6 +40810,7 @@
       <c r="L1509" s="4" t="n"/>
       <c r="M1509" s="4" t="n"/>
       <c r="N1509" s="4" t="n"/>
+      <c r="O1509" s="4" t="n"/>
     </row>
     <row r="1510">
       <c r="A1510" s="5" t="n">
@@ -40798,7 +40819,6 @@
       <c r="B1510" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1510" s="4" t="n"/>
       <c r="D1510" s="4" t="n"/>
       <c r="E1510" s="4" t="n"/>
       <c r="F1510" s="4" t="n"/>
@@ -40810,6 +40830,7 @@
       <c r="L1510" s="4" t="n"/>
       <c r="M1510" s="4" t="n"/>
       <c r="N1510" s="4" t="n"/>
+      <c r="O1510" s="4" t="n"/>
     </row>
     <row r="1511">
       <c r="A1511" s="5" t="n">
@@ -40818,7 +40839,6 @@
       <c r="B1511" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1511" s="4" t="n"/>
       <c r="D1511" s="4" t="n"/>
       <c r="E1511" s="4" t="n"/>
       <c r="F1511" s="4" t="n"/>
@@ -40830,6 +40850,7 @@
       <c r="L1511" s="4" t="n"/>
       <c r="M1511" s="4" t="n"/>
       <c r="N1511" s="4" t="n"/>
+      <c r="O1511" s="4" t="n"/>
     </row>
     <row r="1512">
       <c r="A1512" s="5" t="n">
@@ -40838,7 +40859,6 @@
       <c r="B1512" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1512" s="4" t="n"/>
       <c r="D1512" s="4" t="n"/>
       <c r="E1512" s="4" t="n"/>
       <c r="F1512" s="4" t="n"/>
@@ -40850,6 +40870,7 @@
       <c r="L1512" s="4" t="n"/>
       <c r="M1512" s="4" t="n"/>
       <c r="N1512" s="4" t="n"/>
+      <c r="O1512" s="4" t="n"/>
     </row>
     <row r="1513">
       <c r="A1513" s="5" t="n">
@@ -40858,7 +40879,6 @@
       <c r="B1513" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1513" s="4" t="n"/>
       <c r="D1513" s="4" t="n"/>
       <c r="E1513" s="4" t="n"/>
       <c r="F1513" s="4" t="n"/>
@@ -40870,6 +40890,7 @@
       <c r="L1513" s="4" t="n"/>
       <c r="M1513" s="4" t="n"/>
       <c r="N1513" s="4" t="n"/>
+      <c r="O1513" s="4" t="n"/>
     </row>
     <row r="1514">
       <c r="A1514" s="5" t="n">
@@ -40878,7 +40899,6 @@
       <c r="B1514" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1514" s="4" t="n"/>
       <c r="D1514" s="4" t="n"/>
       <c r="E1514" s="4" t="n"/>
       <c r="F1514" s="4" t="n"/>
@@ -40890,6 +40910,7 @@
       <c r="L1514" s="4" t="n"/>
       <c r="M1514" s="4" t="n"/>
       <c r="N1514" s="4" t="n"/>
+      <c r="O1514" s="4" t="n"/>
     </row>
     <row r="1515">
       <c r="A1515" s="5" t="n">
@@ -40898,7 +40919,6 @@
       <c r="B1515" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1515" s="4" t="n"/>
       <c r="D1515" s="4" t="n"/>
       <c r="E1515" s="4" t="n"/>
       <c r="F1515" s="4" t="n"/>
@@ -40910,6 +40930,7 @@
       <c r="L1515" s="4" t="n"/>
       <c r="M1515" s="4" t="n"/>
       <c r="N1515" s="4" t="n"/>
+      <c r="O1515" s="4" t="n"/>
     </row>
     <row r="1516">
       <c r="A1516" s="6" t="n">
@@ -40918,7 +40939,6 @@
       <c r="B1516" s="7" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1516" s="7" t="n"/>
       <c r="D1516" s="7" t="n"/>
       <c r="E1516" s="7" t="n"/>
       <c r="F1516" s="7" t="n"/>
@@ -40930,6 +40950,7 @@
       <c r="L1516" s="7" t="n"/>
       <c r="M1516" s="7" t="n"/>
       <c r="N1516" s="7" t="n"/>
+      <c r="O1516" s="7" t="n"/>
     </row>
     <row r="1517">
       <c r="A1517" s="5" t="n">
@@ -40938,7 +40959,6 @@
       <c r="B1517" s="3" t="n">
         <v>-67.5</v>
       </c>
-      <c r="C1517" s="4" t="n"/>
       <c r="D1517" s="4" t="n"/>
       <c r="E1517" s="4" t="n"/>
       <c r="F1517" s="4" t="n"/>
@@ -40950,13 +40970,17 @@
       <c r="L1517" s="4" t="n"/>
       <c r="M1517" s="4" t="n"/>
       <c r="N1517" s="4" t="n"/>
+      <c r="O1517" s="4" t="n"/>
     </row>
     <row r="1518">
       <c r="A1518" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B1518" t="n">
-        <v>-75</v>
+        <v>-67.5</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -40970,7 +40994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1535"/>
+  <dimension ref="A1:O1535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40984,62 +41008,67 @@
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jan_Delivery</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Feb_Delivery</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mar_Delivery</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apr_Delivery</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>May_Delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jun_Delivery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jul_Delivery</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Aug_Delivery</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sep_Delivery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Oct_Delivery</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nov_Delivery</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Dec_Delivery</t>
         </is>
@@ -52812,7 +52841,6 @@
       <c r="B1472" s="7" t="n">
         <v>-78.5</v>
       </c>
-      <c r="C1472" s="7" t="n"/>
       <c r="D1472" s="7" t="n"/>
       <c r="E1472" s="7" t="n"/>
       <c r="F1472" s="7" t="n"/>
@@ -52824,6 +52852,7 @@
       <c r="L1472" s="7" t="n"/>
       <c r="M1472" s="7" t="n"/>
       <c r="N1472" s="7" t="n"/>
+      <c r="O1472" s="7" t="n"/>
     </row>
     <row r="1473">
       <c r="A1473" s="6" t="n">
@@ -52832,7 +52861,6 @@
       <c r="B1473" s="7" t="n">
         <v>-78.5</v>
       </c>
-      <c r="C1473" s="7" t="n"/>
       <c r="D1473" s="7" t="n"/>
       <c r="E1473" s="7" t="n"/>
       <c r="F1473" s="7" t="n"/>
@@ -52844,6 +52872,7 @@
       <c r="L1473" s="7" t="n"/>
       <c r="M1473" s="7" t="n"/>
       <c r="N1473" s="7" t="n"/>
+      <c r="O1473" s="7" t="n"/>
     </row>
     <row r="1474">
       <c r="A1474" s="6" t="n">
@@ -52852,7 +52881,6 @@
       <c r="B1474" s="7" t="n">
         <v>-78.5</v>
       </c>
-      <c r="C1474" s="7" t="n"/>
       <c r="D1474" s="7" t="n"/>
       <c r="E1474" s="7" t="n"/>
       <c r="F1474" s="7" t="n"/>
@@ -52864,6 +52892,7 @@
       <c r="L1474" s="7" t="n"/>
       <c r="M1474" s="7" t="n"/>
       <c r="N1474" s="7" t="n"/>
+      <c r="O1474" s="7" t="n"/>
     </row>
     <row r="1475">
       <c r="A1475" s="6" t="n">
@@ -52872,7 +52901,6 @@
       <c r="B1475" s="7" t="n">
         <v>-78.5</v>
       </c>
-      <c r="C1475" s="7" t="n"/>
       <c r="D1475" s="7" t="n"/>
       <c r="E1475" s="7" t="n"/>
       <c r="F1475" s="7" t="n"/>
@@ -52884,6 +52912,7 @@
       <c r="L1475" s="7" t="n"/>
       <c r="M1475" s="7" t="n"/>
       <c r="N1475" s="7" t="n"/>
+      <c r="O1475" s="7" t="n"/>
     </row>
     <row r="1476">
       <c r="A1476" s="6" t="n">
@@ -52892,7 +52921,6 @@
       <c r="B1476" s="7" t="n">
         <v>-78.5</v>
       </c>
-      <c r="C1476" s="7" t="n"/>
       <c r="D1476" s="7" t="n"/>
       <c r="E1476" s="7" t="n"/>
       <c r="F1476" s="7" t="n"/>
@@ -52904,6 +52932,7 @@
       <c r="L1476" s="7" t="n"/>
       <c r="M1476" s="7" t="n"/>
       <c r="N1476" s="7" t="n"/>
+      <c r="O1476" s="7" t="n"/>
     </row>
     <row r="1477">
       <c r="A1477" s="6" t="n">
@@ -52912,7 +52941,6 @@
       <c r="B1477" s="7" t="n">
         <v>-78.5</v>
       </c>
-      <c r="C1477" s="7" t="n"/>
       <c r="D1477" s="7" t="n"/>
       <c r="E1477" s="7" t="n"/>
       <c r="F1477" s="7" t="n"/>
@@ -52924,6 +52952,7 @@
       <c r="L1477" s="7" t="n"/>
       <c r="M1477" s="7" t="n"/>
       <c r="N1477" s="7" t="n"/>
+      <c r="O1477" s="7" t="n"/>
     </row>
     <row r="1478">
       <c r="A1478" s="6" t="n">
@@ -52932,7 +52961,6 @@
       <c r="B1478" s="7" t="n">
         <v>-76</v>
       </c>
-      <c r="C1478" s="7" t="n"/>
       <c r="D1478" s="7" t="n"/>
       <c r="E1478" s="7" t="n"/>
       <c r="F1478" s="7" t="n"/>
@@ -52944,6 +52972,7 @@
       <c r="L1478" s="7" t="n"/>
       <c r="M1478" s="7" t="n"/>
       <c r="N1478" s="7" t="n"/>
+      <c r="O1478" s="7" t="n"/>
     </row>
     <row r="1479">
       <c r="A1479" s="6" t="n">
@@ -52952,7 +52981,6 @@
       <c r="B1479" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1479" s="7" t="n"/>
       <c r="D1479" s="7" t="n"/>
       <c r="E1479" s="7" t="n"/>
       <c r="F1479" s="7" t="n"/>
@@ -52964,6 +52992,7 @@
       <c r="L1479" s="7" t="n"/>
       <c r="M1479" s="7" t="n"/>
       <c r="N1479" s="7" t="n"/>
+      <c r="O1479" s="7" t="n"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6" t="n">
@@ -52972,7 +53001,6 @@
       <c r="B1480" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1480" s="7" t="n"/>
       <c r="D1480" s="7" t="n"/>
       <c r="E1480" s="7" t="n"/>
       <c r="F1480" s="7" t="n"/>
@@ -52984,6 +53012,7 @@
       <c r="L1480" s="7" t="n"/>
       <c r="M1480" s="7" t="n"/>
       <c r="N1480" s="7" t="n"/>
+      <c r="O1480" s="7" t="n"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6" t="n">
@@ -52992,7 +53021,6 @@
       <c r="B1481" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1481" s="7" t="n"/>
       <c r="D1481" s="7" t="n"/>
       <c r="E1481" s="7" t="n"/>
       <c r="F1481" s="7" t="n"/>
@@ -53004,6 +53032,7 @@
       <c r="L1481" s="7" t="n"/>
       <c r="M1481" s="7" t="n"/>
       <c r="N1481" s="7" t="n"/>
+      <c r="O1481" s="7" t="n"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6" t="n">
@@ -53012,7 +53041,6 @@
       <c r="B1482" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1482" s="7" t="n"/>
       <c r="D1482" s="7" t="n"/>
       <c r="E1482" s="7" t="n"/>
       <c r="F1482" s="7" t="n"/>
@@ -53024,6 +53052,7 @@
       <c r="L1482" s="7" t="n"/>
       <c r="M1482" s="7" t="n"/>
       <c r="N1482" s="7" t="n"/>
+      <c r="O1482" s="7" t="n"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6" t="n">
@@ -53032,7 +53061,6 @@
       <c r="B1483" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1483" s="7" t="n"/>
       <c r="D1483" s="7" t="n"/>
       <c r="E1483" s="7" t="n"/>
       <c r="F1483" s="7" t="n"/>
@@ -53044,6 +53072,7 @@
       <c r="L1483" s="7" t="n"/>
       <c r="M1483" s="7" t="n"/>
       <c r="N1483" s="7" t="n"/>
+      <c r="O1483" s="7" t="n"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6" t="n">
@@ -53052,7 +53081,6 @@
       <c r="B1484" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1484" s="7" t="n"/>
       <c r="D1484" s="7" t="n"/>
       <c r="E1484" s="7" t="n"/>
       <c r="F1484" s="7" t="n"/>
@@ -53064,6 +53092,7 @@
       <c r="L1484" s="7" t="n"/>
       <c r="M1484" s="7" t="n"/>
       <c r="N1484" s="7" t="n"/>
+      <c r="O1484" s="7" t="n"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6" t="n">
@@ -53072,7 +53101,6 @@
       <c r="B1485" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1485" s="7" t="n"/>
       <c r="D1485" s="7" t="n"/>
       <c r="E1485" s="7" t="n"/>
       <c r="F1485" s="7" t="n"/>
@@ -53084,6 +53112,7 @@
       <c r="L1485" s="7" t="n"/>
       <c r="M1485" s="7" t="n"/>
       <c r="N1485" s="7" t="n"/>
+      <c r="O1485" s="7" t="n"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6" t="n">
@@ -53092,7 +53121,6 @@
       <c r="B1486" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1486" s="7" t="n"/>
       <c r="D1486" s="7" t="n"/>
       <c r="E1486" s="7" t="n"/>
       <c r="F1486" s="7" t="n"/>
@@ -53104,6 +53132,7 @@
       <c r="L1486" s="7" t="n"/>
       <c r="M1486" s="7" t="n"/>
       <c r="N1486" s="7" t="n"/>
+      <c r="O1486" s="7" t="n"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6" t="n">
@@ -53112,7 +53141,6 @@
       <c r="B1487" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1487" s="7" t="n"/>
       <c r="D1487" s="7" t="n"/>
       <c r="E1487" s="7" t="n"/>
       <c r="F1487" s="7" t="n"/>
@@ -53124,6 +53152,7 @@
       <c r="L1487" s="7" t="n"/>
       <c r="M1487" s="7" t="n"/>
       <c r="N1487" s="7" t="n"/>
+      <c r="O1487" s="7" t="n"/>
     </row>
     <row r="1488">
       <c r="A1488" s="6" t="n">
@@ -53132,7 +53161,6 @@
       <c r="B1488" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1488" s="7" t="n"/>
       <c r="D1488" s="7" t="n"/>
       <c r="E1488" s="7" t="n"/>
       <c r="F1488" s="7" t="n"/>
@@ -53144,6 +53172,7 @@
       <c r="L1488" s="7" t="n"/>
       <c r="M1488" s="7" t="n"/>
       <c r="N1488" s="7" t="n"/>
+      <c r="O1488" s="7" t="n"/>
     </row>
     <row r="1489">
       <c r="A1489" s="6" t="n">
@@ -53152,7 +53181,6 @@
       <c r="B1489" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1489" s="7" t="n"/>
       <c r="D1489" s="7" t="n"/>
       <c r="E1489" s="7" t="n"/>
       <c r="F1489" s="7" t="n"/>
@@ -53164,6 +53192,7 @@
       <c r="L1489" s="7" t="n"/>
       <c r="M1489" s="7" t="n"/>
       <c r="N1489" s="7" t="n"/>
+      <c r="O1489" s="7" t="n"/>
     </row>
     <row r="1490">
       <c r="A1490" s="6" t="n">
@@ -53172,7 +53201,6 @@
       <c r="B1490" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1490" s="7" t="n"/>
       <c r="D1490" s="7" t="n"/>
       <c r="E1490" s="7" t="n"/>
       <c r="F1490" s="7" t="n"/>
@@ -53184,6 +53212,7 @@
       <c r="L1490" s="7" t="n"/>
       <c r="M1490" s="7" t="n"/>
       <c r="N1490" s="7" t="n"/>
+      <c r="O1490" s="7" t="n"/>
     </row>
     <row r="1491">
       <c r="A1491" s="6" t="n">
@@ -53192,7 +53221,6 @@
       <c r="B1491" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1491" s="7" t="n"/>
       <c r="D1491" s="7" t="n"/>
       <c r="E1491" s="7" t="n"/>
       <c r="F1491" s="7" t="n"/>
@@ -53204,6 +53232,7 @@
       <c r="L1491" s="7" t="n"/>
       <c r="M1491" s="7" t="n"/>
       <c r="N1491" s="7" t="n"/>
+      <c r="O1491" s="7" t="n"/>
     </row>
     <row r="1492">
       <c r="A1492" s="6" t="n">
@@ -53212,7 +53241,6 @@
       <c r="B1492" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1492" s="7" t="n"/>
       <c r="D1492" s="7" t="n"/>
       <c r="E1492" s="7" t="n"/>
       <c r="F1492" s="7" t="n"/>
@@ -53224,6 +53252,7 @@
       <c r="L1492" s="7" t="n"/>
       <c r="M1492" s="7" t="n"/>
       <c r="N1492" s="7" t="n"/>
+      <c r="O1492" s="7" t="n"/>
     </row>
     <row r="1493">
       <c r="A1493" s="6" t="n">
@@ -53232,7 +53261,6 @@
       <c r="B1493" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1493" s="7" t="n"/>
       <c r="D1493" s="7" t="n"/>
       <c r="E1493" s="7" t="n"/>
       <c r="F1493" s="7" t="n"/>
@@ -53244,6 +53272,7 @@
       <c r="L1493" s="7" t="n"/>
       <c r="M1493" s="7" t="n"/>
       <c r="N1493" s="7" t="n"/>
+      <c r="O1493" s="7" t="n"/>
     </row>
     <row r="1494">
       <c r="A1494" s="6" t="n">
@@ -53252,7 +53281,6 @@
       <c r="B1494" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1494" s="7" t="n"/>
       <c r="D1494" s="7" t="n"/>
       <c r="E1494" s="7" t="n"/>
       <c r="F1494" s="7" t="n"/>
@@ -53264,6 +53292,7 @@
       <c r="L1494" s="7" t="n"/>
       <c r="M1494" s="7" t="n"/>
       <c r="N1494" s="7" t="n"/>
+      <c r="O1494" s="7" t="n"/>
     </row>
     <row r="1495">
       <c r="A1495" s="6" t="n">
@@ -53272,7 +53301,6 @@
       <c r="B1495" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1495" s="7" t="n"/>
       <c r="D1495" s="7" t="n"/>
       <c r="E1495" s="7" t="n"/>
       <c r="F1495" s="7" t="n"/>
@@ -53284,6 +53312,7 @@
       <c r="L1495" s="7" t="n"/>
       <c r="M1495" s="7" t="n"/>
       <c r="N1495" s="7" t="n"/>
+      <c r="O1495" s="7" t="n"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6" t="n">
@@ -53292,7 +53321,6 @@
       <c r="B1496" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1496" s="7" t="n"/>
       <c r="D1496" s="7" t="n"/>
       <c r="E1496" s="7" t="n"/>
       <c r="F1496" s="7" t="n"/>
@@ -53304,6 +53332,7 @@
       <c r="L1496" s="7" t="n"/>
       <c r="M1496" s="7" t="n"/>
       <c r="N1496" s="7" t="n"/>
+      <c r="O1496" s="7" t="n"/>
     </row>
     <row r="1497">
       <c r="A1497" s="6" t="n">
@@ -53312,7 +53341,6 @@
       <c r="B1497" s="7" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1497" s="7" t="n"/>
       <c r="D1497" s="7" t="n"/>
       <c r="E1497" s="7" t="n"/>
       <c r="F1497" s="7" t="n"/>
@@ -53324,6 +53352,7 @@
       <c r="L1497" s="7" t="n"/>
       <c r="M1497" s="7" t="n"/>
       <c r="N1497" s="7" t="n"/>
+      <c r="O1497" s="7" t="n"/>
     </row>
     <row r="1498">
       <c r="A1498" s="6" t="n">
@@ -53332,7 +53361,6 @@
       <c r="B1498" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1498" s="7" t="n"/>
       <c r="D1498" s="7" t="n"/>
       <c r="E1498" s="7" t="n"/>
       <c r="F1498" s="7" t="n"/>
@@ -53344,6 +53372,7 @@
       <c r="L1498" s="7" t="n"/>
       <c r="M1498" s="7" t="n"/>
       <c r="N1498" s="7" t="n"/>
+      <c r="O1498" s="7" t="n"/>
     </row>
     <row r="1499">
       <c r="A1499" s="6" t="n">
@@ -53352,7 +53381,6 @@
       <c r="B1499" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1499" s="7" t="n"/>
       <c r="D1499" s="7" t="n"/>
       <c r="E1499" s="7" t="n"/>
       <c r="F1499" s="7" t="n"/>
@@ -53364,6 +53392,7 @@
       <c r="L1499" s="7" t="n"/>
       <c r="M1499" s="7" t="n"/>
       <c r="N1499" s="7" t="n"/>
+      <c r="O1499" s="7" t="n"/>
     </row>
     <row r="1500">
       <c r="A1500" s="6" t="n">
@@ -53372,7 +53401,6 @@
       <c r="B1500" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1500" s="7" t="n"/>
       <c r="D1500" s="7" t="n"/>
       <c r="E1500" s="7" t="n"/>
       <c r="F1500" s="7" t="n"/>
@@ -53384,6 +53412,7 @@
       <c r="L1500" s="7" t="n"/>
       <c r="M1500" s="7" t="n"/>
       <c r="N1500" s="7" t="n"/>
+      <c r="O1500" s="7" t="n"/>
     </row>
     <row r="1501">
       <c r="A1501" s="6" t="n">
@@ -53392,7 +53421,6 @@
       <c r="B1501" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1501" s="7" t="n"/>
       <c r="D1501" s="7" t="n"/>
       <c r="E1501" s="7" t="n"/>
       <c r="F1501" s="7" t="n"/>
@@ -53404,6 +53432,7 @@
       <c r="L1501" s="7" t="n"/>
       <c r="M1501" s="7" t="n"/>
       <c r="N1501" s="7" t="n"/>
+      <c r="O1501" s="7" t="n"/>
     </row>
     <row r="1502">
       <c r="A1502" s="6" t="n">
@@ -53412,7 +53441,6 @@
       <c r="B1502" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1502" s="7" t="n"/>
       <c r="D1502" s="7" t="n"/>
       <c r="E1502" s="7" t="n"/>
       <c r="F1502" s="7" t="n"/>
@@ -53424,6 +53452,7 @@
       <c r="L1502" s="7" t="n"/>
       <c r="M1502" s="7" t="n"/>
       <c r="N1502" s="7" t="n"/>
+      <c r="O1502" s="7" t="n"/>
     </row>
     <row r="1503">
       <c r="A1503" s="6" t="n">
@@ -53432,7 +53461,6 @@
       <c r="B1503" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1503" s="7" t="n"/>
       <c r="D1503" s="7" t="n"/>
       <c r="E1503" s="7" t="n"/>
       <c r="F1503" s="7" t="n"/>
@@ -53444,6 +53472,7 @@
       <c r="L1503" s="7" t="n"/>
       <c r="M1503" s="7" t="n"/>
       <c r="N1503" s="7" t="n"/>
+      <c r="O1503" s="7" t="n"/>
     </row>
     <row r="1504">
       <c r="A1504" s="6" t="n">
@@ -53452,7 +53481,6 @@
       <c r="B1504" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1504" s="7" t="n"/>
       <c r="D1504" s="7" t="n"/>
       <c r="E1504" s="7" t="n"/>
       <c r="F1504" s="7" t="n"/>
@@ -53464,6 +53492,7 @@
       <c r="L1504" s="7" t="n"/>
       <c r="M1504" s="7" t="n"/>
       <c r="N1504" s="7" t="n"/>
+      <c r="O1504" s="7" t="n"/>
     </row>
     <row r="1505">
       <c r="A1505" s="6" t="n">
@@ -53472,7 +53501,6 @@
       <c r="B1505" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1505" s="7" t="n"/>
       <c r="D1505" s="7" t="n"/>
       <c r="E1505" s="7" t="n"/>
       <c r="F1505" s="7" t="n"/>
@@ -53484,6 +53512,7 @@
       <c r="L1505" s="7" t="n"/>
       <c r="M1505" s="7" t="n"/>
       <c r="N1505" s="7" t="n"/>
+      <c r="O1505" s="7" t="n"/>
     </row>
     <row r="1506">
       <c r="A1506" s="6" t="n">
@@ -53492,7 +53521,6 @@
       <c r="B1506" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1506" s="7" t="n"/>
       <c r="D1506" s="7" t="n"/>
       <c r="E1506" s="7" t="n"/>
       <c r="F1506" s="7" t="n"/>
@@ -53504,6 +53532,7 @@
       <c r="L1506" s="7" t="n"/>
       <c r="M1506" s="7" t="n"/>
       <c r="N1506" s="7" t="n"/>
+      <c r="O1506" s="7" t="n"/>
     </row>
     <row r="1507">
       <c r="A1507" s="6" t="n">
@@ -53512,7 +53541,6 @@
       <c r="B1507" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1507" s="7" t="n"/>
       <c r="D1507" s="7" t="n"/>
       <c r="E1507" s="7" t="n"/>
       <c r="F1507" s="7" t="n"/>
@@ -53524,6 +53552,7 @@
       <c r="L1507" s="7" t="n"/>
       <c r="M1507" s="7" t="n"/>
       <c r="N1507" s="7" t="n"/>
+      <c r="O1507" s="7" t="n"/>
     </row>
     <row r="1508">
       <c r="A1508" s="6" t="n">
@@ -53532,7 +53561,6 @@
       <c r="B1508" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1508" s="7" t="n"/>
       <c r="D1508" s="7" t="n"/>
       <c r="E1508" s="7" t="n"/>
       <c r="F1508" s="7" t="n"/>
@@ -53544,6 +53572,7 @@
       <c r="L1508" s="7" t="n"/>
       <c r="M1508" s="7" t="n"/>
       <c r="N1508" s="7" t="n"/>
+      <c r="O1508" s="7" t="n"/>
     </row>
     <row r="1509">
       <c r="A1509" s="6" t="n">
@@ -53552,7 +53581,6 @@
       <c r="B1509" s="7" t="n">
         <v>-68.5</v>
       </c>
-      <c r="C1509" s="7" t="n"/>
       <c r="D1509" s="7" t="n"/>
       <c r="E1509" s="7" t="n"/>
       <c r="F1509" s="7" t="n"/>
@@ -53564,6 +53592,7 @@
       <c r="L1509" s="7" t="n"/>
       <c r="M1509" s="7" t="n"/>
       <c r="N1509" s="7" t="n"/>
+      <c r="O1509" s="7" t="n"/>
     </row>
     <row r="1510">
       <c r="A1510" s="5" t="n">
@@ -53572,7 +53601,6 @@
       <c r="B1510" s="3" t="n">
         <v>-71</v>
       </c>
-      <c r="C1510" s="4" t="n"/>
       <c r="D1510" s="4" t="n"/>
       <c r="E1510" s="4" t="n"/>
       <c r="F1510" s="4" t="n"/>
@@ -53584,6 +53612,7 @@
       <c r="L1510" s="4" t="n"/>
       <c r="M1510" s="4" t="n"/>
       <c r="N1510" s="4" t="n"/>
+      <c r="O1510" s="4" t="n"/>
     </row>
     <row r="1511">
       <c r="A1511" s="5" t="n">
@@ -53592,7 +53621,6 @@
       <c r="B1511" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1511" s="4" t="n"/>
       <c r="D1511" s="4" t="n"/>
       <c r="E1511" s="4" t="n"/>
       <c r="F1511" s="4" t="n"/>
@@ -53604,6 +53632,7 @@
       <c r="L1511" s="4" t="n"/>
       <c r="M1511" s="4" t="n"/>
       <c r="N1511" s="4" t="n"/>
+      <c r="O1511" s="4" t="n"/>
     </row>
     <row r="1512">
       <c r="A1512" s="5" t="n">
@@ -53612,7 +53641,6 @@
       <c r="B1512" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1512" s="4" t="n"/>
       <c r="D1512" s="4" t="n"/>
       <c r="E1512" s="4" t="n"/>
       <c r="F1512" s="4" t="n"/>
@@ -53624,6 +53652,7 @@
       <c r="L1512" s="4" t="n"/>
       <c r="M1512" s="4" t="n"/>
       <c r="N1512" s="4" t="n"/>
+      <c r="O1512" s="4" t="n"/>
     </row>
     <row r="1513">
       <c r="A1513" s="6" t="n">
@@ -53632,7 +53661,6 @@
       <c r="B1513" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1513" s="7" t="n"/>
       <c r="D1513" s="7" t="n"/>
       <c r="E1513" s="7" t="n"/>
       <c r="F1513" s="7" t="n"/>
@@ -53644,6 +53672,7 @@
       <c r="L1513" s="7" t="n"/>
       <c r="M1513" s="7" t="n"/>
       <c r="N1513" s="7" t="n"/>
+      <c r="O1513" s="7" t="n"/>
     </row>
     <row r="1514">
       <c r="A1514" s="6" t="n">
@@ -53652,7 +53681,6 @@
       <c r="B1514" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1514" s="7" t="n"/>
       <c r="D1514" s="7" t="n"/>
       <c r="E1514" s="7" t="n"/>
       <c r="F1514" s="7" t="n"/>
@@ -53664,6 +53692,7 @@
       <c r="L1514" s="7" t="n"/>
       <c r="M1514" s="7" t="n"/>
       <c r="N1514" s="7" t="n"/>
+      <c r="O1514" s="7" t="n"/>
     </row>
     <row r="1515">
       <c r="A1515" s="5" t="n">
@@ -53672,7 +53701,6 @@
       <c r="B1515" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1515" s="4" t="n"/>
       <c r="D1515" s="4" t="n"/>
       <c r="E1515" s="4" t="n"/>
       <c r="F1515" s="4" t="n"/>
@@ -53684,6 +53712,7 @@
       <c r="L1515" s="4" t="n"/>
       <c r="M1515" s="4" t="n"/>
       <c r="N1515" s="4" t="n"/>
+      <c r="O1515" s="4" t="n"/>
     </row>
     <row r="1516">
       <c r="A1516" s="5" t="n">
@@ -53692,7 +53721,6 @@
       <c r="B1516" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1516" s="4" t="n"/>
       <c r="D1516" s="4" t="n"/>
       <c r="E1516" s="4" t="n"/>
       <c r="F1516" s="4" t="n"/>
@@ -53704,6 +53732,7 @@
       <c r="L1516" s="4" t="n"/>
       <c r="M1516" s="4" t="n"/>
       <c r="N1516" s="4" t="n"/>
+      <c r="O1516" s="4" t="n"/>
     </row>
     <row r="1517">
       <c r="A1517" s="5" t="n">
@@ -53712,7 +53741,6 @@
       <c r="B1517" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1517" s="4" t="n"/>
       <c r="D1517" s="4" t="n"/>
       <c r="E1517" s="4" t="n"/>
       <c r="F1517" s="4" t="n"/>
@@ -53724,6 +53752,7 @@
       <c r="L1517" s="4" t="n"/>
       <c r="M1517" s="4" t="n"/>
       <c r="N1517" s="4" t="n"/>
+      <c r="O1517" s="4" t="n"/>
     </row>
     <row r="1518">
       <c r="A1518" s="5" t="n">
@@ -53732,7 +53761,6 @@
       <c r="B1518" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1518" s="4" t="n"/>
       <c r="D1518" s="4" t="n"/>
       <c r="E1518" s="4" t="n"/>
       <c r="F1518" s="4" t="n"/>
@@ -53744,6 +53772,7 @@
       <c r="L1518" s="4" t="n"/>
       <c r="M1518" s="4" t="n"/>
       <c r="N1518" s="4" t="n"/>
+      <c r="O1518" s="4" t="n"/>
     </row>
     <row r="1519">
       <c r="A1519" s="6" t="n">
@@ -53752,7 +53781,6 @@
       <c r="B1519" s="7" t="n">
         <v>-75</v>
       </c>
-      <c r="C1519" s="7" t="n"/>
       <c r="D1519" s="7" t="n"/>
       <c r="E1519" s="7" t="n"/>
       <c r="F1519" s="7" t="n"/>
@@ -53764,6 +53792,7 @@
       <c r="L1519" s="7" t="n"/>
       <c r="M1519" s="7" t="n"/>
       <c r="N1519" s="7" t="n"/>
+      <c r="O1519" s="7" t="n"/>
     </row>
     <row r="1520">
       <c r="A1520" s="5" t="n">
@@ -53772,7 +53801,6 @@
       <c r="B1520" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1520" s="4" t="n"/>
       <c r="D1520" s="4" t="n"/>
       <c r="E1520" s="4" t="n"/>
       <c r="F1520" s="4" t="n"/>
@@ -53784,6 +53812,7 @@
       <c r="L1520" s="4" t="n"/>
       <c r="M1520" s="4" t="n"/>
       <c r="N1520" s="4" t="n"/>
+      <c r="O1520" s="4" t="n"/>
     </row>
     <row r="1521">
       <c r="A1521" s="5" t="n">
@@ -53792,7 +53821,6 @@
       <c r="B1521" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1521" s="4" t="n"/>
       <c r="D1521" s="4" t="n"/>
       <c r="E1521" s="4" t="n"/>
       <c r="F1521" s="4" t="n"/>
@@ -53804,6 +53832,7 @@
       <c r="L1521" s="4" t="n"/>
       <c r="M1521" s="4" t="n"/>
       <c r="N1521" s="4" t="n"/>
+      <c r="O1521" s="4" t="n"/>
     </row>
     <row r="1522">
       <c r="A1522" s="5" t="n">
@@ -53812,7 +53841,6 @@
       <c r="B1522" s="3" t="n">
         <v>-70</v>
       </c>
-      <c r="C1522" s="4" t="n"/>
       <c r="D1522" s="4" t="n"/>
       <c r="E1522" s="4" t="n"/>
       <c r="F1522" s="4" t="n"/>
@@ -53824,6 +53852,7 @@
       <c r="L1522" s="4" t="n"/>
       <c r="M1522" s="4" t="n"/>
       <c r="N1522" s="4" t="n"/>
+      <c r="O1522" s="4" t="n"/>
     </row>
     <row r="1523">
       <c r="A1523" s="6" t="n">
@@ -53832,7 +53861,6 @@
       <c r="B1523" s="7" t="n">
         <v>-70</v>
       </c>
-      <c r="C1523" s="7" t="n"/>
       <c r="D1523" s="7" t="n"/>
       <c r="E1523" s="7" t="n"/>
       <c r="F1523" s="7" t="n"/>
@@ -53844,6 +53872,7 @@
       <c r="L1523" s="7" t="n"/>
       <c r="M1523" s="7" t="n"/>
       <c r="N1523" s="7" t="n"/>
+      <c r="O1523" s="7" t="n"/>
     </row>
     <row r="1524">
       <c r="A1524" s="5" t="n">
@@ -53852,7 +53881,6 @@
       <c r="B1524" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1524" s="4" t="n"/>
       <c r="D1524" s="4" t="n"/>
       <c r="E1524" s="4" t="n"/>
       <c r="F1524" s="4" t="n"/>
@@ -53864,6 +53892,7 @@
       <c r="L1524" s="4" t="n"/>
       <c r="M1524" s="4" t="n"/>
       <c r="N1524" s="4" t="n"/>
+      <c r="O1524" s="4" t="n"/>
     </row>
     <row r="1525">
       <c r="A1525" s="5" t="n">
@@ -53872,7 +53901,6 @@
       <c r="B1525" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1525" s="4" t="n"/>
       <c r="D1525" s="4" t="n"/>
       <c r="E1525" s="4" t="n"/>
       <c r="F1525" s="4" t="n"/>
@@ -53884,6 +53912,7 @@
       <c r="L1525" s="4" t="n"/>
       <c r="M1525" s="4" t="n"/>
       <c r="N1525" s="4" t="n"/>
+      <c r="O1525" s="4" t="n"/>
     </row>
     <row r="1526">
       <c r="A1526" s="5" t="n">
@@ -53892,7 +53921,6 @@
       <c r="B1526" s="3" t="n">
         <v>-72.5</v>
       </c>
-      <c r="C1526" s="4" t="n"/>
       <c r="D1526" s="4" t="n"/>
       <c r="E1526" s="4" t="n"/>
       <c r="F1526" s="4" t="n"/>
@@ -53904,6 +53932,7 @@
       <c r="L1526" s="4" t="n"/>
       <c r="M1526" s="4" t="n"/>
       <c r="N1526" s="4" t="n"/>
+      <c r="O1526" s="4" t="n"/>
     </row>
     <row r="1527">
       <c r="A1527" s="5" t="n">
@@ -53912,7 +53941,6 @@
       <c r="B1527" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1527" s="4" t="n"/>
       <c r="D1527" s="4" t="n"/>
       <c r="E1527" s="4" t="n"/>
       <c r="F1527" s="4" t="n"/>
@@ -53924,6 +53952,7 @@
       <c r="L1527" s="4" t="n"/>
       <c r="M1527" s="4" t="n"/>
       <c r="N1527" s="4" t="n"/>
+      <c r="O1527" s="4" t="n"/>
     </row>
     <row r="1528">
       <c r="A1528" s="5" t="n">
@@ -53932,7 +53961,6 @@
       <c r="B1528" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1528" s="4" t="n"/>
       <c r="D1528" s="4" t="n"/>
       <c r="E1528" s="4" t="n"/>
       <c r="F1528" s="4" t="n"/>
@@ -53944,6 +53972,7 @@
       <c r="L1528" s="4" t="n"/>
       <c r="M1528" s="4" t="n"/>
       <c r="N1528" s="4" t="n"/>
+      <c r="O1528" s="4" t="n"/>
     </row>
     <row r="1529">
       <c r="A1529" s="5" t="n">
@@ -53952,7 +53981,6 @@
       <c r="B1529" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1529" s="4" t="n"/>
       <c r="D1529" s="4" t="n"/>
       <c r="E1529" s="4" t="n"/>
       <c r="F1529" s="4" t="n"/>
@@ -53964,6 +53992,7 @@
       <c r="L1529" s="4" t="n"/>
       <c r="M1529" s="4" t="n"/>
       <c r="N1529" s="4" t="n"/>
+      <c r="O1529" s="4" t="n"/>
     </row>
     <row r="1530">
       <c r="A1530" s="5" t="n">
@@ -53972,7 +54001,6 @@
       <c r="B1530" s="3" t="n">
         <v>-75</v>
       </c>
-      <c r="C1530" s="4" t="n"/>
       <c r="D1530" s="4" t="n"/>
       <c r="E1530" s="4" t="n"/>
       <c r="F1530" s="4" t="n"/>
@@ -53984,6 +54012,7 @@
       <c r="L1530" s="4" t="n"/>
       <c r="M1530" s="4" t="n"/>
       <c r="N1530" s="4" t="n"/>
+      <c r="O1530" s="4" t="n"/>
     </row>
     <row r="1531">
       <c r="A1531" s="5" t="n">
@@ -53992,7 +54021,6 @@
       <c r="B1531" s="3" t="n">
         <v>-76</v>
       </c>
-      <c r="C1531" s="4" t="n"/>
       <c r="D1531" s="4" t="n"/>
       <c r="E1531" s="4" t="n"/>
       <c r="F1531" s="4" t="n"/>
@@ -54004,6 +54032,7 @@
       <c r="L1531" s="4" t="n"/>
       <c r="M1531" s="4" t="n"/>
       <c r="N1531" s="4" t="n"/>
+      <c r="O1531" s="4" t="n"/>
     </row>
     <row r="1532">
       <c r="A1532" s="5" t="n">
@@ -54012,7 +54041,6 @@
       <c r="B1532" s="3" t="n">
         <v>-76</v>
       </c>
-      <c r="C1532" s="4" t="n"/>
       <c r="D1532" s="4" t="n"/>
       <c r="E1532" s="4" t="n"/>
       <c r="F1532" s="4" t="n"/>
@@ -54024,6 +54052,7 @@
       <c r="L1532" s="4" t="n"/>
       <c r="M1532" s="4" t="n"/>
       <c r="N1532" s="4" t="n"/>
+      <c r="O1532" s="4" t="n"/>
     </row>
     <row r="1533">
       <c r="A1533" s="6" t="n">
@@ -54032,7 +54061,6 @@
       <c r="B1533" s="7" t="n">
         <v>-77</v>
       </c>
-      <c r="C1533" s="7" t="n"/>
       <c r="D1533" s="7" t="n"/>
       <c r="E1533" s="7" t="n"/>
       <c r="F1533" s="7" t="n"/>
@@ -54044,6 +54072,7 @@
       <c r="L1533" s="7" t="n"/>
       <c r="M1533" s="7" t="n"/>
       <c r="N1533" s="7" t="n"/>
+      <c r="O1533" s="7" t="n"/>
     </row>
     <row r="1534">
       <c r="A1534" s="5" t="n">
@@ -54052,7 +54081,6 @@
       <c r="B1534" s="3" t="n">
         <v>-81</v>
       </c>
-      <c r="C1534" s="4" t="n"/>
       <c r="D1534" s="4" t="n"/>
       <c r="E1534" s="4" t="n"/>
       <c r="F1534" s="4" t="n"/>
@@ -54064,13 +54092,17 @@
       <c r="L1534" s="4" t="n"/>
       <c r="M1534" s="4" t="n"/>
       <c r="N1534" s="4" t="n"/>
+      <c r="O1534" s="4" t="n"/>
     </row>
     <row r="1535">
       <c r="A1535" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B1535" t="n">
-        <v>-85.5</v>
+        <v>-81</v>
+      </c>
+      <c r="C1535" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -54084,7 +54116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1536"/>
+  <dimension ref="A1:O1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54098,62 +54130,67 @@
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jan_Delivery</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Feb_Delivery</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mar_Delivery</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apr_Delivery</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>May_Delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jun_Delivery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jul_Delivery</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Aug_Delivery</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sep_Delivery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Oct_Delivery</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nov_Delivery</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Dec_Delivery</t>
         </is>
@@ -65934,7 +65971,6 @@
       <c r="B1473" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1473" s="7" t="n"/>
       <c r="D1473" s="7" t="n"/>
       <c r="E1473" s="7" t="n"/>
       <c r="F1473" s="7" t="n"/>
@@ -65946,6 +65982,7 @@
       <c r="L1473" s="7" t="n"/>
       <c r="M1473" s="7" t="n"/>
       <c r="N1473" s="7" t="n"/>
+      <c r="O1473" s="7" t="n"/>
     </row>
     <row r="1474">
       <c r="A1474" s="6" t="n">
@@ -65954,7 +65991,6 @@
       <c r="B1474" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1474" s="7" t="n"/>
       <c r="D1474" s="7" t="n"/>
       <c r="E1474" s="7" t="n"/>
       <c r="F1474" s="7" t="n"/>
@@ -65966,6 +66002,7 @@
       <c r="L1474" s="7" t="n"/>
       <c r="M1474" s="7" t="n"/>
       <c r="N1474" s="7" t="n"/>
+      <c r="O1474" s="7" t="n"/>
     </row>
     <row r="1475">
       <c r="A1475" s="6" t="n">
@@ -65974,7 +66011,6 @@
       <c r="B1475" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1475" s="7" t="n"/>
       <c r="D1475" s="7" t="n"/>
       <c r="E1475" s="7" t="n"/>
       <c r="F1475" s="7" t="n"/>
@@ -65986,6 +66022,7 @@
       <c r="L1475" s="7" t="n"/>
       <c r="M1475" s="7" t="n"/>
       <c r="N1475" s="7" t="n"/>
+      <c r="O1475" s="7" t="n"/>
     </row>
     <row r="1476">
       <c r="A1476" s="6" t="n">
@@ -65994,7 +66031,6 @@
       <c r="B1476" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1476" s="7" t="n"/>
       <c r="D1476" s="7" t="n"/>
       <c r="E1476" s="7" t="n"/>
       <c r="F1476" s="7" t="n"/>
@@ -66006,6 +66042,7 @@
       <c r="L1476" s="7" t="n"/>
       <c r="M1476" s="7" t="n"/>
       <c r="N1476" s="7" t="n"/>
+      <c r="O1476" s="7" t="n"/>
     </row>
     <row r="1477">
       <c r="A1477" s="6" t="n">
@@ -66014,7 +66051,6 @@
       <c r="B1477" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1477" s="7" t="n"/>
       <c r="D1477" s="7" t="n"/>
       <c r="E1477" s="7" t="n"/>
       <c r="F1477" s="7" t="n"/>
@@ -66026,6 +66062,7 @@
       <c r="L1477" s="7" t="n"/>
       <c r="M1477" s="7" t="n"/>
       <c r="N1477" s="7" t="n"/>
+      <c r="O1477" s="7" t="n"/>
     </row>
     <row r="1478">
       <c r="A1478" s="6" t="n">
@@ -66034,7 +66071,6 @@
       <c r="B1478" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1478" s="7" t="n"/>
       <c r="D1478" s="7" t="n"/>
       <c r="E1478" s="7" t="n"/>
       <c r="F1478" s="7" t="n"/>
@@ -66046,6 +66082,7 @@
       <c r="L1478" s="7" t="n"/>
       <c r="M1478" s="7" t="n"/>
       <c r="N1478" s="7" t="n"/>
+      <c r="O1478" s="7" t="n"/>
     </row>
     <row r="1479">
       <c r="A1479" s="6" t="n">
@@ -66054,7 +66091,6 @@
       <c r="B1479" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1479" s="7" t="n"/>
       <c r="D1479" s="7" t="n"/>
       <c r="E1479" s="7" t="n"/>
       <c r="F1479" s="7" t="n"/>
@@ -66066,6 +66102,7 @@
       <c r="L1479" s="7" t="n"/>
       <c r="M1479" s="7" t="n"/>
       <c r="N1479" s="7" t="n"/>
+      <c r="O1479" s="7" t="n"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6" t="n">
@@ -66074,7 +66111,6 @@
       <c r="B1480" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1480" s="7" t="n"/>
       <c r="D1480" s="7" t="n"/>
       <c r="E1480" s="7" t="n"/>
       <c r="F1480" s="7" t="n"/>
@@ -66086,6 +66122,7 @@
       <c r="L1480" s="7" t="n"/>
       <c r="M1480" s="7" t="n"/>
       <c r="N1480" s="7" t="n"/>
+      <c r="O1480" s="7" t="n"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6" t="n">
@@ -66094,7 +66131,6 @@
       <c r="B1481" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1481" s="7" t="n"/>
       <c r="D1481" s="7" t="n"/>
       <c r="E1481" s="7" t="n"/>
       <c r="F1481" s="7" t="n"/>
@@ -66106,6 +66142,7 @@
       <c r="L1481" s="7" t="n"/>
       <c r="M1481" s="7" t="n"/>
       <c r="N1481" s="7" t="n"/>
+      <c r="O1481" s="7" t="n"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6" t="n">
@@ -66114,7 +66151,6 @@
       <c r="B1482" s="7" t="n">
         <v>-35</v>
       </c>
-      <c r="C1482" s="7" t="n"/>
       <c r="D1482" s="7" t="n"/>
       <c r="E1482" s="7" t="n"/>
       <c r="F1482" s="7" t="n"/>
@@ -66126,6 +66162,7 @@
       <c r="L1482" s="7" t="n"/>
       <c r="M1482" s="7" t="n"/>
       <c r="N1482" s="7" t="n"/>
+      <c r="O1482" s="7" t="n"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6" t="n">
@@ -66134,7 +66171,6 @@
       <c r="B1483" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1483" s="7" t="n"/>
       <c r="D1483" s="7" t="n"/>
       <c r="E1483" s="7" t="n"/>
       <c r="F1483" s="7" t="n"/>
@@ -66146,6 +66182,7 @@
       <c r="L1483" s="7" t="n"/>
       <c r="M1483" s="7" t="n"/>
       <c r="N1483" s="7" t="n"/>
+      <c r="O1483" s="7" t="n"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6" t="n">
@@ -66154,7 +66191,6 @@
       <c r="B1484" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1484" s="7" t="n"/>
       <c r="D1484" s="7" t="n"/>
       <c r="E1484" s="7" t="n"/>
       <c r="F1484" s="7" t="n"/>
@@ -66166,6 +66202,7 @@
       <c r="L1484" s="7" t="n"/>
       <c r="M1484" s="7" t="n"/>
       <c r="N1484" s="7" t="n"/>
+      <c r="O1484" s="7" t="n"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6" t="n">
@@ -66174,7 +66211,6 @@
       <c r="B1485" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1485" s="7" t="n"/>
       <c r="D1485" s="7" t="n"/>
       <c r="E1485" s="7" t="n"/>
       <c r="F1485" s="7" t="n"/>
@@ -66186,6 +66222,7 @@
       <c r="L1485" s="7" t="n"/>
       <c r="M1485" s="7" t="n"/>
       <c r="N1485" s="7" t="n"/>
+      <c r="O1485" s="7" t="n"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6" t="n">
@@ -66194,7 +66231,6 @@
       <c r="B1486" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1486" s="7" t="n"/>
       <c r="D1486" s="7" t="n"/>
       <c r="E1486" s="7" t="n"/>
       <c r="F1486" s="7" t="n"/>
@@ -66206,6 +66242,7 @@
       <c r="L1486" s="7" t="n"/>
       <c r="M1486" s="7" t="n"/>
       <c r="N1486" s="7" t="n"/>
+      <c r="O1486" s="7" t="n"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6" t="n">
@@ -66214,7 +66251,6 @@
       <c r="B1487" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1487" s="7" t="n"/>
       <c r="D1487" s="7" t="n"/>
       <c r="E1487" s="7" t="n"/>
       <c r="F1487" s="7" t="n"/>
@@ -66226,6 +66262,7 @@
       <c r="L1487" s="7" t="n"/>
       <c r="M1487" s="7" t="n"/>
       <c r="N1487" s="7" t="n"/>
+      <c r="O1487" s="7" t="n"/>
     </row>
     <row r="1488">
       <c r="A1488" s="6" t="n">
@@ -66234,7 +66271,6 @@
       <c r="B1488" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1488" s="7" t="n"/>
       <c r="D1488" s="7" t="n"/>
       <c r="E1488" s="7" t="n"/>
       <c r="F1488" s="7" t="n"/>
@@ -66246,6 +66282,7 @@
       <c r="L1488" s="7" t="n"/>
       <c r="M1488" s="7" t="n"/>
       <c r="N1488" s="7" t="n"/>
+      <c r="O1488" s="7" t="n"/>
     </row>
     <row r="1489">
       <c r="A1489" s="6" t="n">
@@ -66254,7 +66291,6 @@
       <c r="B1489" s="7" t="n">
         <v>-30</v>
       </c>
-      <c r="C1489" s="7" t="n"/>
       <c r="D1489" s="7" t="n"/>
       <c r="E1489" s="7" t="n"/>
       <c r="F1489" s="7" t="n"/>
@@ -66266,6 +66302,7 @@
       <c r="L1489" s="7" t="n"/>
       <c r="M1489" s="7" t="n"/>
       <c r="N1489" s="7" t="n"/>
+      <c r="O1489" s="7" t="n"/>
     </row>
     <row r="1490">
       <c r="A1490" s="6" t="n">
@@ -66274,7 +66311,6 @@
       <c r="B1490" s="7" t="n">
         <v>-25</v>
       </c>
-      <c r="C1490" s="7" t="n"/>
       <c r="D1490" s="7" t="n"/>
       <c r="E1490" s="7" t="n"/>
       <c r="F1490" s="7" t="n"/>
@@ -66286,6 +66322,7 @@
       <c r="L1490" s="7" t="n"/>
       <c r="M1490" s="7" t="n"/>
       <c r="N1490" s="7" t="n"/>
+      <c r="O1490" s="7" t="n"/>
     </row>
     <row r="1491">
       <c r="A1491" s="6" t="n">
@@ -66294,7 +66331,6 @@
       <c r="B1491" s="7" t="n">
         <v>-25</v>
       </c>
-      <c r="C1491" s="7" t="n"/>
       <c r="D1491" s="7" t="n"/>
       <c r="E1491" s="7" t="n"/>
       <c r="F1491" s="7" t="n"/>
@@ -66306,6 +66342,7 @@
       <c r="L1491" s="7" t="n"/>
       <c r="M1491" s="7" t="n"/>
       <c r="N1491" s="7" t="n"/>
+      <c r="O1491" s="7" t="n"/>
     </row>
     <row r="1492">
       <c r="A1492" s="6" t="n">
@@ -66314,7 +66351,6 @@
       <c r="B1492" s="7" t="n">
         <v>-25</v>
       </c>
-      <c r="C1492" s="7" t="n"/>
       <c r="D1492" s="7" t="n"/>
       <c r="E1492" s="7" t="n"/>
       <c r="F1492" s="7" t="n"/>
@@ -66326,6 +66362,7 @@
       <c r="L1492" s="7" t="n"/>
       <c r="M1492" s="7" t="n"/>
       <c r="N1492" s="7" t="n"/>
+      <c r="O1492" s="7" t="n"/>
     </row>
     <row r="1493">
       <c r="A1493" s="6" t="n">
@@ -66334,7 +66371,6 @@
       <c r="B1493" s="7" t="n">
         <v>-25</v>
       </c>
-      <c r="C1493" s="7" t="n"/>
       <c r="D1493" s="7" t="n"/>
       <c r="E1493" s="7" t="n"/>
       <c r="F1493" s="7" t="n"/>
@@ -66346,6 +66382,7 @@
       <c r="L1493" s="7" t="n"/>
       <c r="M1493" s="7" t="n"/>
       <c r="N1493" s="7" t="n"/>
+      <c r="O1493" s="7" t="n"/>
     </row>
     <row r="1494">
       <c r="A1494" s="6" t="n">
@@ -66354,7 +66391,6 @@
       <c r="B1494" s="7" t="n">
         <v>-14</v>
       </c>
-      <c r="C1494" s="7" t="n"/>
       <c r="D1494" s="7" t="n"/>
       <c r="E1494" s="7" t="n"/>
       <c r="F1494" s="7" t="n"/>
@@ -66366,6 +66402,7 @@
       <c r="L1494" s="7" t="n"/>
       <c r="M1494" s="7" t="n"/>
       <c r="N1494" s="7" t="n"/>
+      <c r="O1494" s="7" t="n"/>
     </row>
     <row r="1495">
       <c r="A1495" s="6" t="n">
@@ -66374,7 +66411,6 @@
       <c r="B1495" s="7" t="n">
         <v>-9</v>
       </c>
-      <c r="C1495" s="7" t="n"/>
       <c r="D1495" s="7" t="n"/>
       <c r="E1495" s="7" t="n"/>
       <c r="F1495" s="7" t="n"/>
@@ -66386,6 +66422,7 @@
       <c r="L1495" s="7" t="n"/>
       <c r="M1495" s="7" t="n"/>
       <c r="N1495" s="7" t="n"/>
+      <c r="O1495" s="7" t="n"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6" t="n">
@@ -66394,7 +66431,6 @@
       <c r="B1496" s="7" t="n">
         <v>-9</v>
       </c>
-      <c r="C1496" s="7" t="n"/>
       <c r="D1496" s="7" t="n"/>
       <c r="E1496" s="7" t="n"/>
       <c r="F1496" s="7" t="n"/>
@@ -66406,6 +66442,7 @@
       <c r="L1496" s="7" t="n"/>
       <c r="M1496" s="7" t="n"/>
       <c r="N1496" s="7" t="n"/>
+      <c r="O1496" s="7" t="n"/>
     </row>
     <row r="1497">
       <c r="A1497" s="6" t="n">
@@ -66414,7 +66451,6 @@
       <c r="B1497" s="7" t="n">
         <v>-9</v>
       </c>
-      <c r="C1497" s="7" t="n"/>
       <c r="D1497" s="7" t="n"/>
       <c r="E1497" s="7" t="n"/>
       <c r="F1497" s="7" t="n"/>
@@ -66426,6 +66462,7 @@
       <c r="L1497" s="7" t="n"/>
       <c r="M1497" s="7" t="n"/>
       <c r="N1497" s="7" t="n"/>
+      <c r="O1497" s="7" t="n"/>
     </row>
     <row r="1498">
       <c r="A1498" s="6" t="n">
@@ -66434,7 +66471,6 @@
       <c r="B1498" s="7" t="n">
         <v>-9</v>
       </c>
-      <c r="C1498" s="7" t="n"/>
       <c r="D1498" s="7" t="n"/>
       <c r="E1498" s="7" t="n"/>
       <c r="F1498" s="7" t="n"/>
@@ -66446,6 +66482,7 @@
       <c r="L1498" s="7" t="n"/>
       <c r="M1498" s="7" t="n"/>
       <c r="N1498" s="7" t="n"/>
+      <c r="O1498" s="7" t="n"/>
     </row>
     <row r="1499">
       <c r="A1499" s="6" t="n">
@@ -66454,7 +66491,6 @@
       <c r="B1499" s="7" t="n">
         <v>-9</v>
       </c>
-      <c r="C1499" s="7" t="n"/>
       <c r="D1499" s="7" t="n"/>
       <c r="E1499" s="7" t="n"/>
       <c r="F1499" s="7" t="n"/>
@@ -66466,6 +66502,7 @@
       <c r="L1499" s="7" t="n"/>
       <c r="M1499" s="7" t="n"/>
       <c r="N1499" s="7" t="n"/>
+      <c r="O1499" s="7" t="n"/>
     </row>
     <row r="1500">
       <c r="A1500" s="6" t="n">
@@ -66474,7 +66511,6 @@
       <c r="B1500" s="7" t="n">
         <v>-9</v>
       </c>
-      <c r="C1500" s="7" t="n"/>
       <c r="D1500" s="7" t="n"/>
       <c r="E1500" s="7" t="n"/>
       <c r="F1500" s="7" t="n"/>
@@ -66486,6 +66522,7 @@
       <c r="L1500" s="7" t="n"/>
       <c r="M1500" s="7" t="n"/>
       <c r="N1500" s="7" t="n"/>
+      <c r="O1500" s="7" t="n"/>
     </row>
     <row r="1501">
       <c r="A1501" s="6" t="n">
@@ -66494,7 +66531,6 @@
       <c r="B1501" s="7" t="n">
         <v>-15</v>
       </c>
-      <c r="C1501" s="7" t="n"/>
       <c r="D1501" s="7" t="n"/>
       <c r="E1501" s="7" t="n"/>
       <c r="F1501" s="7" t="n"/>
@@ -66506,6 +66542,7 @@
       <c r="L1501" s="7" t="n"/>
       <c r="M1501" s="7" t="n"/>
       <c r="N1501" s="7" t="n"/>
+      <c r="O1501" s="7" t="n"/>
     </row>
     <row r="1502">
       <c r="A1502" s="6" t="n">
@@ -66514,7 +66551,6 @@
       <c r="B1502" s="7" t="n">
         <v>-16.5</v>
       </c>
-      <c r="C1502" s="7" t="n"/>
       <c r="D1502" s="7" t="n"/>
       <c r="E1502" s="7" t="n"/>
       <c r="F1502" s="7" t="n"/>
@@ -66526,6 +66562,7 @@
       <c r="L1502" s="7" t="n"/>
       <c r="M1502" s="7" t="n"/>
       <c r="N1502" s="7" t="n"/>
+      <c r="O1502" s="7" t="n"/>
     </row>
     <row r="1503">
       <c r="A1503" s="6" t="n">
@@ -66534,7 +66571,6 @@
       <c r="B1503" s="7" t="n">
         <v>-16.5</v>
       </c>
-      <c r="C1503" s="7" t="n"/>
       <c r="D1503" s="7" t="n"/>
       <c r="E1503" s="7" t="n"/>
       <c r="F1503" s="7" t="n"/>
@@ -66546,6 +66582,7 @@
       <c r="L1503" s="7" t="n"/>
       <c r="M1503" s="7" t="n"/>
       <c r="N1503" s="7" t="n"/>
+      <c r="O1503" s="7" t="n"/>
     </row>
     <row r="1504">
       <c r="A1504" s="6" t="n">
@@ -66554,7 +66591,6 @@
       <c r="B1504" s="7" t="n">
         <v>-45</v>
       </c>
-      <c r="C1504" s="7" t="n"/>
       <c r="D1504" s="7" t="n"/>
       <c r="E1504" s="7" t="n"/>
       <c r="F1504" s="7" t="n"/>
@@ -66566,6 +66602,7 @@
       <c r="L1504" s="7" t="n"/>
       <c r="M1504" s="7" t="n"/>
       <c r="N1504" s="7" t="n"/>
+      <c r="O1504" s="7" t="n"/>
     </row>
     <row r="1505">
       <c r="A1505" s="6" t="n">
@@ -66574,7 +66611,6 @@
       <c r="B1505" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1505" s="7" t="n"/>
       <c r="D1505" s="7" t="n"/>
       <c r="E1505" s="7" t="n"/>
       <c r="F1505" s="7" t="n"/>
@@ -66586,6 +66622,7 @@
       <c r="L1505" s="7" t="n"/>
       <c r="M1505" s="7" t="n"/>
       <c r="N1505" s="7" t="n"/>
+      <c r="O1505" s="7" t="n"/>
     </row>
     <row r="1506">
       <c r="A1506" s="6" t="n">
@@ -66594,7 +66631,6 @@
       <c r="B1506" s="7" t="n">
         <v>-32.5</v>
       </c>
-      <c r="C1506" s="7" t="n"/>
       <c r="D1506" s="7" t="n"/>
       <c r="E1506" s="7" t="n"/>
       <c r="F1506" s="7" t="n"/>
@@ -66606,6 +66642,7 @@
       <c r="L1506" s="7" t="n"/>
       <c r="M1506" s="7" t="n"/>
       <c r="N1506" s="7" t="n"/>
+      <c r="O1506" s="7" t="n"/>
     </row>
     <row r="1507">
       <c r="A1507" s="6" t="n">
@@ -66614,7 +66651,6 @@
       <c r="B1507" s="7" t="n">
         <v>-42.5</v>
       </c>
-      <c r="C1507" s="7" t="n"/>
       <c r="D1507" s="7" t="n"/>
       <c r="E1507" s="7" t="n"/>
       <c r="F1507" s="7" t="n"/>
@@ -66626,6 +66662,7 @@
       <c r="L1507" s="7" t="n"/>
       <c r="M1507" s="7" t="n"/>
       <c r="N1507" s="7" t="n"/>
+      <c r="O1507" s="7" t="n"/>
     </row>
     <row r="1508">
       <c r="A1508" s="6" t="n">
@@ -66634,7 +66671,6 @@
       <c r="B1508" s="7" t="n">
         <v>-42.5</v>
       </c>
-      <c r="C1508" s="7" t="n"/>
       <c r="D1508" s="7" t="n"/>
       <c r="E1508" s="7" t="n"/>
       <c r="F1508" s="7" t="n"/>
@@ -66646,6 +66682,7 @@
       <c r="L1508" s="7" t="n"/>
       <c r="M1508" s="7" t="n"/>
       <c r="N1508" s="7" t="n"/>
+      <c r="O1508" s="7" t="n"/>
     </row>
     <row r="1509">
       <c r="A1509" s="6" t="n">
@@ -66654,7 +66691,6 @@
       <c r="B1509" s="7" t="n">
         <v>-42.5</v>
       </c>
-      <c r="C1509" s="7" t="n"/>
       <c r="D1509" s="7" t="n"/>
       <c r="E1509" s="7" t="n"/>
       <c r="F1509" s="7" t="n"/>
@@ -66666,6 +66702,7 @@
       <c r="L1509" s="7" t="n"/>
       <c r="M1509" s="7" t="n"/>
       <c r="N1509" s="7" t="n"/>
+      <c r="O1509" s="7" t="n"/>
     </row>
     <row r="1510">
       <c r="A1510" s="6" t="n">
@@ -66674,7 +66711,6 @@
       <c r="B1510" s="7" t="n">
         <v>-42.5</v>
       </c>
-      <c r="C1510" s="7" t="n"/>
       <c r="D1510" s="7" t="n"/>
       <c r="E1510" s="7" t="n"/>
       <c r="F1510" s="7" t="n"/>
@@ -66686,6 +66722,7 @@
       <c r="L1510" s="7" t="n"/>
       <c r="M1510" s="7" t="n"/>
       <c r="N1510" s="7" t="n"/>
+      <c r="O1510" s="7" t="n"/>
     </row>
     <row r="1511">
       <c r="A1511" s="5" t="n">
@@ -66694,7 +66731,6 @@
       <c r="B1511" s="3" t="n">
         <v>-42.5</v>
       </c>
-      <c r="C1511" s="4" t="n"/>
       <c r="D1511" s="4" t="n"/>
       <c r="E1511" s="4" t="n"/>
       <c r="F1511" s="4" t="n"/>
@@ -66706,6 +66742,7 @@
       <c r="L1511" s="4" t="n"/>
       <c r="M1511" s="4" t="n"/>
       <c r="N1511" s="4" t="n"/>
+      <c r="O1511" s="4" t="n"/>
     </row>
     <row r="1512">
       <c r="A1512" s="5" t="n">
@@ -66714,7 +66751,6 @@
       <c r="B1512" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1512" s="4" t="n"/>
       <c r="D1512" s="4" t="n"/>
       <c r="E1512" s="4" t="n"/>
       <c r="F1512" s="4" t="n"/>
@@ -66726,6 +66762,7 @@
       <c r="L1512" s="4" t="n"/>
       <c r="M1512" s="4" t="n"/>
       <c r="N1512" s="4" t="n"/>
+      <c r="O1512" s="4" t="n"/>
     </row>
     <row r="1513">
       <c r="A1513" s="5" t="n">
@@ -66734,7 +66771,6 @@
       <c r="B1513" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1513" s="4" t="n"/>
       <c r="D1513" s="4" t="n"/>
       <c r="E1513" s="4" t="n"/>
       <c r="F1513" s="4" t="n"/>
@@ -66746,6 +66782,7 @@
       <c r="L1513" s="4" t="n"/>
       <c r="M1513" s="4" t="n"/>
       <c r="N1513" s="4" t="n"/>
+      <c r="O1513" s="4" t="n"/>
     </row>
     <row r="1514">
       <c r="A1514" s="6" t="n">
@@ -66754,7 +66791,6 @@
       <c r="B1514" s="7" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1514" s="7" t="n"/>
       <c r="D1514" s="7" t="n"/>
       <c r="E1514" s="7" t="n"/>
       <c r="F1514" s="7" t="n"/>
@@ -66766,6 +66802,7 @@
       <c r="L1514" s="7" t="n"/>
       <c r="M1514" s="7" t="n"/>
       <c r="N1514" s="7" t="n"/>
+      <c r="O1514" s="7" t="n"/>
     </row>
     <row r="1515">
       <c r="A1515" s="6" t="n">
@@ -66774,7 +66811,6 @@
       <c r="B1515" s="7" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1515" s="7" t="n"/>
       <c r="D1515" s="7" t="n"/>
       <c r="E1515" s="7" t="n"/>
       <c r="F1515" s="7" t="n"/>
@@ -66786,6 +66822,7 @@
       <c r="L1515" s="7" t="n"/>
       <c r="M1515" s="7" t="n"/>
       <c r="N1515" s="7" t="n"/>
+      <c r="O1515" s="7" t="n"/>
     </row>
     <row r="1516">
       <c r="A1516" s="5" t="n">
@@ -66794,7 +66831,6 @@
       <c r="B1516" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1516" s="4" t="n"/>
       <c r="D1516" s="4" t="n"/>
       <c r="E1516" s="4" t="n"/>
       <c r="F1516" s="4" t="n"/>
@@ -66806,6 +66842,7 @@
       <c r="L1516" s="4" t="n"/>
       <c r="M1516" s="4" t="n"/>
       <c r="N1516" s="4" t="n"/>
+      <c r="O1516" s="4" t="n"/>
     </row>
     <row r="1517">
       <c r="A1517" s="5" t="n">
@@ -66814,7 +66851,6 @@
       <c r="B1517" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1517" s="4" t="n"/>
       <c r="D1517" s="4" t="n"/>
       <c r="E1517" s="4" t="n"/>
       <c r="F1517" s="4" t="n"/>
@@ -66826,6 +66862,7 @@
       <c r="L1517" s="4" t="n"/>
       <c r="M1517" s="4" t="n"/>
       <c r="N1517" s="4" t="n"/>
+      <c r="O1517" s="4" t="n"/>
     </row>
     <row r="1518">
       <c r="A1518" s="5" t="n">
@@ -66834,7 +66871,6 @@
       <c r="B1518" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1518" s="4" t="n"/>
       <c r="D1518" s="4" t="n"/>
       <c r="E1518" s="4" t="n"/>
       <c r="F1518" s="4" t="n"/>
@@ -66846,6 +66882,7 @@
       <c r="L1518" s="4" t="n"/>
       <c r="M1518" s="4" t="n"/>
       <c r="N1518" s="4" t="n"/>
+      <c r="O1518" s="4" t="n"/>
     </row>
     <row r="1519">
       <c r="A1519" s="5" t="n">
@@ -66854,7 +66891,6 @@
       <c r="B1519" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1519" s="4" t="n"/>
       <c r="D1519" s="4" t="n"/>
       <c r="E1519" s="4" t="n"/>
       <c r="F1519" s="4" t="n"/>
@@ -66866,6 +66902,7 @@
       <c r="L1519" s="4" t="n"/>
       <c r="M1519" s="4" t="n"/>
       <c r="N1519" s="4" t="n"/>
+      <c r="O1519" s="4" t="n"/>
     </row>
     <row r="1520">
       <c r="A1520" s="6" t="n">
@@ -66874,7 +66911,6 @@
       <c r="B1520" s="7" t="n">
         <v>-47.5</v>
       </c>
-      <c r="C1520" s="7" t="n"/>
       <c r="D1520" s="7" t="n"/>
       <c r="E1520" s="7" t="n"/>
       <c r="F1520" s="7" t="n"/>
@@ -66886,6 +66922,7 @@
       <c r="L1520" s="7" t="n"/>
       <c r="M1520" s="7" t="n"/>
       <c r="N1520" s="7" t="n"/>
+      <c r="O1520" s="7" t="n"/>
     </row>
     <row r="1521">
       <c r="A1521" s="5" t="n">
@@ -66894,7 +66931,6 @@
       <c r="B1521" s="3" t="n">
         <v>-47.5</v>
       </c>
-      <c r="C1521" s="4" t="n"/>
       <c r="D1521" s="4" t="n"/>
       <c r="E1521" s="4" t="n"/>
       <c r="F1521" s="4" t="n"/>
@@ -66906,6 +66942,7 @@
       <c r="L1521" s="4" t="n"/>
       <c r="M1521" s="4" t="n"/>
       <c r="N1521" s="4" t="n"/>
+      <c r="O1521" s="4" t="n"/>
     </row>
     <row r="1522">
       <c r="A1522" s="5" t="n">
@@ -66914,7 +66951,6 @@
       <c r="B1522" s="3" t="n">
         <v>-32</v>
       </c>
-      <c r="C1522" s="4" t="n"/>
       <c r="D1522" s="4" t="n"/>
       <c r="E1522" s="4" t="n"/>
       <c r="F1522" s="4" t="n"/>
@@ -66926,6 +66962,7 @@
       <c r="L1522" s="4" t="n"/>
       <c r="M1522" s="4" t="n"/>
       <c r="N1522" s="4" t="n"/>
+      <c r="O1522" s="4" t="n"/>
     </row>
     <row r="1523">
       <c r="A1523" s="5" t="n">
@@ -66934,7 +66971,6 @@
       <c r="B1523" s="3" t="n">
         <v>-32</v>
       </c>
-      <c r="C1523" s="4" t="n"/>
       <c r="D1523" s="4" t="n"/>
       <c r="E1523" s="4" t="n"/>
       <c r="F1523" s="4" t="n"/>
@@ -66946,6 +66982,7 @@
       <c r="L1523" s="4" t="n"/>
       <c r="M1523" s="4" t="n"/>
       <c r="N1523" s="4" t="n"/>
+      <c r="O1523" s="4" t="n"/>
     </row>
     <row r="1524">
       <c r="A1524" s="6" t="n">
@@ -66954,7 +66991,6 @@
       <c r="B1524" s="7" t="n">
         <v>-32</v>
       </c>
-      <c r="C1524" s="7" t="n"/>
       <c r="D1524" s="7" t="n"/>
       <c r="E1524" s="7" t="n"/>
       <c r="F1524" s="7" t="n"/>
@@ -66966,6 +67002,7 @@
       <c r="L1524" s="7" t="n"/>
       <c r="M1524" s="7" t="n"/>
       <c r="N1524" s="7" t="n"/>
+      <c r="O1524" s="7" t="n"/>
     </row>
     <row r="1525">
       <c r="A1525" s="5" t="n">
@@ -66974,7 +67011,6 @@
       <c r="B1525" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1525" s="4" t="n"/>
       <c r="D1525" s="4" t="n"/>
       <c r="E1525" s="4" t="n"/>
       <c r="F1525" s="4" t="n"/>
@@ -66986,6 +67022,7 @@
       <c r="L1525" s="4" t="n"/>
       <c r="M1525" s="4" t="n"/>
       <c r="N1525" s="4" t="n"/>
+      <c r="O1525" s="4" t="n"/>
     </row>
     <row r="1526">
       <c r="A1526" s="5" t="n">
@@ -66994,7 +67031,6 @@
       <c r="B1526" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1526" s="4" t="n"/>
       <c r="D1526" s="4" t="n"/>
       <c r="E1526" s="4" t="n"/>
       <c r="F1526" s="4" t="n"/>
@@ -67006,6 +67042,7 @@
       <c r="L1526" s="4" t="n"/>
       <c r="M1526" s="4" t="n"/>
       <c r="N1526" s="4" t="n"/>
+      <c r="O1526" s="4" t="n"/>
     </row>
     <row r="1527">
       <c r="A1527" s="5" t="n">
@@ -67014,7 +67051,6 @@
       <c r="B1527" s="3" t="n">
         <v>-47.5</v>
       </c>
-      <c r="C1527" s="4" t="n"/>
       <c r="D1527" s="4" t="n"/>
       <c r="E1527" s="4" t="n"/>
       <c r="F1527" s="4" t="n"/>
@@ -67026,6 +67062,7 @@
       <c r="L1527" s="4" t="n"/>
       <c r="M1527" s="4" t="n"/>
       <c r="N1527" s="4" t="n"/>
+      <c r="O1527" s="4" t="n"/>
     </row>
     <row r="1528">
       <c r="A1528" s="5" t="n">
@@ -67034,7 +67071,6 @@
       <c r="B1528" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1528" s="4" t="n"/>
       <c r="D1528" s="4" t="n"/>
       <c r="E1528" s="4" t="n"/>
       <c r="F1528" s="4" t="n"/>
@@ -67046,6 +67082,7 @@
       <c r="L1528" s="4" t="n"/>
       <c r="M1528" s="4" t="n"/>
       <c r="N1528" s="4" t="n"/>
+      <c r="O1528" s="4" t="n"/>
     </row>
     <row r="1529">
       <c r="A1529" s="5" t="n">
@@ -67054,7 +67091,6 @@
       <c r="B1529" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1529" s="4" t="n"/>
       <c r="D1529" s="4" t="n"/>
       <c r="E1529" s="4" t="n"/>
       <c r="F1529" s="4" t="n"/>
@@ -67066,6 +67102,7 @@
       <c r="L1529" s="4" t="n"/>
       <c r="M1529" s="4" t="n"/>
       <c r="N1529" s="4" t="n"/>
+      <c r="O1529" s="4" t="n"/>
     </row>
     <row r="1530">
       <c r="A1530" s="5" t="n">
@@ -67074,7 +67111,6 @@
       <c r="B1530" s="3" t="n">
         <v>-49.5</v>
       </c>
-      <c r="C1530" s="4" t="n"/>
       <c r="D1530" s="4" t="n"/>
       <c r="E1530" s="4" t="n"/>
       <c r="F1530" s="4" t="n"/>
@@ -67086,6 +67122,7 @@
       <c r="L1530" s="4" t="n"/>
       <c r="M1530" s="4" t="n"/>
       <c r="N1530" s="4" t="n"/>
+      <c r="O1530" s="4" t="n"/>
     </row>
     <row r="1531">
       <c r="A1531" s="5" t="n">
@@ -67094,7 +67131,6 @@
       <c r="B1531" s="3" t="n">
         <v>-50</v>
       </c>
-      <c r="C1531" s="4" t="n"/>
       <c r="D1531" s="4" t="n"/>
       <c r="E1531" s="4" t="n"/>
       <c r="F1531" s="4" t="n"/>
@@ -67106,6 +67142,7 @@
       <c r="L1531" s="4" t="n"/>
       <c r="M1531" s="4" t="n"/>
       <c r="N1531" s="4" t="n"/>
+      <c r="O1531" s="4" t="n"/>
     </row>
     <row r="1532">
       <c r="A1532" s="5" t="n">
@@ -67114,7 +67151,6 @@
       <c r="B1532" s="3" t="n">
         <v>-50</v>
       </c>
-      <c r="C1532" s="4" t="n"/>
       <c r="D1532" s="4" t="n"/>
       <c r="E1532" s="4" t="n"/>
       <c r="F1532" s="4" t="n"/>
@@ -67126,6 +67162,7 @@
       <c r="L1532" s="4" t="n"/>
       <c r="M1532" s="4" t="n"/>
       <c r="N1532" s="4" t="n"/>
+      <c r="O1532" s="4" t="n"/>
     </row>
     <row r="1533">
       <c r="A1533" s="5" t="n">
@@ -67134,7 +67171,6 @@
       <c r="B1533" s="3" t="n">
         <v>-52.5</v>
       </c>
-      <c r="C1533" s="4" t="n"/>
       <c r="D1533" s="4" t="n"/>
       <c r="E1533" s="4" t="n"/>
       <c r="F1533" s="4" t="n"/>
@@ -67146,6 +67182,7 @@
       <c r="L1533" s="4" t="n"/>
       <c r="M1533" s="4" t="n"/>
       <c r="N1533" s="4" t="n"/>
+      <c r="O1533" s="4" t="n"/>
     </row>
     <row r="1534">
       <c r="A1534" s="6" t="n">
@@ -67154,7 +67191,6 @@
       <c r="B1534" s="7" t="n">
         <v>-50</v>
       </c>
-      <c r="C1534" s="7" t="n"/>
       <c r="D1534" s="7" t="n"/>
       <c r="E1534" s="7" t="n"/>
       <c r="F1534" s="7" t="n"/>
@@ -67166,6 +67202,7 @@
       <c r="L1534" s="7" t="n"/>
       <c r="M1534" s="7" t="n"/>
       <c r="N1534" s="7" t="n"/>
+      <c r="O1534" s="7" t="n"/>
     </row>
     <row r="1535">
       <c r="A1535" s="5" t="n">
@@ -67174,7 +67211,6 @@
       <c r="B1535" s="3" t="n">
         <v>-50</v>
       </c>
-      <c r="C1535" s="4" t="n"/>
       <c r="D1535" s="4" t="n"/>
       <c r="E1535" s="4" t="n"/>
       <c r="F1535" s="4" t="n"/>
@@ -67186,6 +67222,7 @@
       <c r="L1535" s="4" t="n"/>
       <c r="M1535" s="4" t="n"/>
       <c r="N1535" s="4" t="n"/>
+      <c r="O1535" s="4" t="n"/>
     </row>
     <row r="1536">
       <c r="A1536" s="8" t="n">
@@ -67193,6 +67230,9 @@
       </c>
       <c r="B1536" t="n">
         <v>-50</v>
+      </c>
+      <c r="C1536" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/玉米大豆历史数据/大豆基差/South Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/South Dakota Basis.xlsx
@@ -1900,7 +1900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1522"/>
+  <dimension ref="A1:O1524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14922,6 +14922,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1523">
+      <c r="A1523" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1523" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C1523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1524" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14933,7 +14955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1541"/>
+  <dimension ref="A1:O1543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28107,6 +28129,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1542">
+      <c r="A1542" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1542" t="n">
+        <v>-59</v>
+      </c>
+      <c r="C1542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1543" t="n">
+        <v>-59</v>
+      </c>
+      <c r="C1543" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28118,7 +28162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1523"/>
+  <dimension ref="A1:O1525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41148,6 +41192,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1524">
+      <c r="A1524" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1524" t="n">
+        <v>-67.5</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1525" t="n">
+        <v>-67.5</v>
+      </c>
+      <c r="C1525" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41159,7 +41225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1540"/>
+  <dimension ref="A1:O1542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54325,6 +54391,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1541">
+      <c r="A1541" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1541" t="n">
+        <v>-81</v>
+      </c>
+      <c r="C1541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1542" t="n">
+        <v>-88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54336,7 +54421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1541"/>
+  <dimension ref="A1:O1543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67508,6 +67593,28 @@
       </c>
       <c r="C1541" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1542" t="n">
+        <v>-52</v>
+      </c>
+      <c r="C1542" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1543" t="n">
+        <v>-50</v>
+      </c>
+      <c r="C1543" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
